--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ip_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ip_calibrated.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="252">
   <si>
     <t>subsector</t>
   </si>
@@ -45,6 +45,174 @@
   </si>
   <si>
     <t>min_55</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t>IPPU</t>
@@ -994,181 +1162,181 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2</v>
-      </c>
-      <c r="M1" s="1">
-        <v>3</v>
-      </c>
-      <c r="N1" s="1">
-        <v>4</v>
-      </c>
-      <c r="O1" s="1">
-        <v>5</v>
-      </c>
-      <c r="P1" s="1">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>7</v>
-      </c>
-      <c r="R1" s="1">
-        <v>8</v>
-      </c>
-      <c r="S1" s="1">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="1">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="1">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="1">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="1">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="1">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="1">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="1">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="1">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="1">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="1">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="1">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="1">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" s="1">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="1">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AV1" s="1">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="1">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="1">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AY1" s="1">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="1">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BA1" s="1">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BB1" s="1">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BC1" s="1">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BD1" s="1">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BE1" s="1">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BF1" s="1">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BG1" s="1">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BH1" s="1">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BI1" s="1">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BJ1" s="1">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BK1" s="1">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BL1" s="1">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BM1" s="1">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:65">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1347,10 +1515,10 @@
     </row>
     <row r="3" spans="1:65">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1529,10 +1697,10 @@
     </row>
     <row r="4" spans="1:65">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="H4">
         <v>1.5</v>
@@ -1711,10 +1879,10 @@
     </row>
     <row r="5" spans="1:65">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="H5">
         <v>1.5</v>
@@ -1893,10 +2061,10 @@
     </row>
     <row r="6" spans="1:65">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="H6">
         <v>1.5</v>
@@ -2075,10 +2243,10 @@
     </row>
     <row r="7" spans="1:65">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="H7">
         <v>1.5</v>
@@ -2257,10 +2425,10 @@
     </row>
     <row r="8" spans="1:65">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="H8">
         <v>1.5</v>
@@ -2439,10 +2607,10 @@
     </row>
     <row r="9" spans="1:65">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="H9">
         <v>1.5</v>
@@ -2621,10 +2789,10 @@
     </row>
     <row r="10" spans="1:65">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="H10">
         <v>1.5</v>
@@ -2803,10 +2971,10 @@
     </row>
     <row r="11" spans="1:65">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="H11">
         <v>1.5</v>
@@ -2985,10 +3153,10 @@
     </row>
     <row r="12" spans="1:65">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="H12">
         <v>1.5</v>
@@ -3167,10 +3335,10 @@
     </row>
     <row r="13" spans="1:65">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="H13">
         <v>1.5</v>
@@ -3349,10 +3517,10 @@
     </row>
     <row r="14" spans="1:65">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="H14">
         <v>1.5</v>
@@ -3531,10 +3699,10 @@
     </row>
     <row r="15" spans="1:65">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="H15">
         <v>1.5</v>
@@ -3713,10 +3881,10 @@
     </row>
     <row r="16" spans="1:65">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="H16">
         <v>1.5</v>
@@ -3895,10 +4063,10 @@
     </row>
     <row r="17" spans="1:65">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="H17">
         <v>1.5</v>
@@ -4077,10 +4245,10 @@
     </row>
     <row r="18" spans="1:65">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="H18">
         <v>1.5</v>
@@ -4259,10 +4427,10 @@
     </row>
     <row r="19" spans="1:65">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="H19">
         <v>1.5</v>
@@ -4441,10 +4609,10 @@
     </row>
     <row r="20" spans="1:65">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="H20">
         <v>1.5</v>
@@ -4623,10 +4791,10 @@
     </row>
     <row r="21" spans="1:65">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="H21">
         <v>1.5</v>
@@ -4805,10 +4973,10 @@
     </row>
     <row r="22" spans="1:65">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="H22">
         <v>1.5</v>
@@ -4987,10 +5155,10 @@
     </row>
     <row r="23" spans="1:65">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="H23">
         <v>1.5</v>
@@ -5169,10 +5337,10 @@
     </row>
     <row r="24" spans="1:65">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -5351,10 +5519,10 @@
     </row>
     <row r="25" spans="1:65">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -5533,10 +5701,10 @@
     </row>
     <row r="26" spans="1:65">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -5715,10 +5883,10 @@
     </row>
     <row r="27" spans="1:65">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -5897,10 +6065,10 @@
     </row>
     <row r="28" spans="1:65">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -6079,10 +6247,10 @@
     </row>
     <row r="29" spans="1:65">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -6261,10 +6429,10 @@
     </row>
     <row r="30" spans="1:65">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -6443,10 +6611,10 @@
     </row>
     <row r="31" spans="1:65">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -6625,10 +6793,10 @@
     </row>
     <row r="32" spans="1:65">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -6807,10 +6975,10 @@
     </row>
     <row r="33" spans="1:65">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -6989,10 +7157,10 @@
     </row>
     <row r="34" spans="1:65">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -7171,10 +7339,10 @@
     </row>
     <row r="35" spans="1:65">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -7353,10 +7521,10 @@
     </row>
     <row r="36" spans="1:65">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -7535,10 +7703,10 @@
     </row>
     <row r="37" spans="1:65">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -7717,10 +7885,10 @@
     </row>
     <row r="38" spans="1:65">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -7899,10 +8067,10 @@
     </row>
     <row r="39" spans="1:65">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -8081,10 +8249,10 @@
     </row>
     <row r="40" spans="1:65">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -8263,10 +8431,10 @@
     </row>
     <row r="41" spans="1:65">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -8445,10 +8613,10 @@
     </row>
     <row r="42" spans="1:65">
       <c r="A42" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -8627,10 +8795,10 @@
     </row>
     <row r="43" spans="1:65">
       <c r="A43" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -8809,10 +8977,10 @@
     </row>
     <row r="44" spans="1:65">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B44" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -8991,10 +9159,10 @@
     </row>
     <row r="45" spans="1:65">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -9173,10 +9341,10 @@
     </row>
     <row r="46" spans="1:65">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -9355,10 +9523,10 @@
     </row>
     <row r="47" spans="1:65">
       <c r="A47" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -9537,10 +9705,10 @@
     </row>
     <row r="48" spans="1:65">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -9719,10 +9887,10 @@
     </row>
     <row r="49" spans="1:65">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -9901,10 +10069,10 @@
     </row>
     <row r="50" spans="1:65">
       <c r="A50" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -10083,10 +10251,10 @@
     </row>
     <row r="51" spans="1:65">
       <c r="A51" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B51" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -10265,10 +10433,10 @@
     </row>
     <row r="52" spans="1:65">
       <c r="A52" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B52" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -10447,10 +10615,10 @@
     </row>
     <row r="53" spans="1:65">
       <c r="A53" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -10629,10 +10797,10 @@
     </row>
     <row r="54" spans="1:65">
       <c r="A54" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B54" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -10811,10 +10979,10 @@
     </row>
     <row r="55" spans="1:65">
       <c r="A55" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -10993,10 +11161,10 @@
     </row>
     <row r="56" spans="1:65">
       <c r="A56" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -11175,10 +11343,10 @@
     </row>
     <row r="57" spans="1:65">
       <c r="A57" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B57" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="H57">
         <v>1</v>
@@ -11357,10 +11525,10 @@
     </row>
     <row r="58" spans="1:65">
       <c r="A58" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="H58">
         <v>1</v>
@@ -11539,10 +11707,10 @@
     </row>
     <row r="59" spans="1:65">
       <c r="A59" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -11721,10 +11889,10 @@
     </row>
     <row r="60" spans="1:65">
       <c r="A60" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -11903,10 +12071,10 @@
     </row>
     <row r="61" spans="1:65">
       <c r="A61" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B61" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -12085,10 +12253,10 @@
     </row>
     <row r="62" spans="1:65">
       <c r="A62" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -12267,10 +12435,10 @@
     </row>
     <row r="63" spans="1:65">
       <c r="A63" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -12449,10 +12617,10 @@
     </row>
     <row r="64" spans="1:65">
       <c r="A64" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -12631,10 +12799,10 @@
     </row>
     <row r="65" spans="1:65">
       <c r="A65" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -12813,10 +12981,10 @@
     </row>
     <row r="66" spans="1:65">
       <c r="A66" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -12995,10 +13163,10 @@
     </row>
     <row r="67" spans="1:65">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -13177,10 +13345,10 @@
     </row>
     <row r="68" spans="1:65">
       <c r="A68" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B68" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -13359,10 +13527,10 @@
     </row>
     <row r="69" spans="1:65">
       <c r="A69" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B69" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -13541,10 +13709,10 @@
     </row>
     <row r="70" spans="1:65">
       <c r="A70" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B70" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -13723,10 +13891,10 @@
     </row>
     <row r="71" spans="1:65">
       <c r="A71" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -13905,10 +14073,10 @@
     </row>
     <row r="72" spans="1:65">
       <c r="A72" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B72" t="s">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="H72">
         <v>1</v>
@@ -14087,10 +14255,10 @@
     </row>
     <row r="73" spans="1:65">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B73" t="s">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -14269,10 +14437,10 @@
     </row>
     <row r="74" spans="1:65">
       <c r="A74" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B74" t="s">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -14451,10 +14619,10 @@
     </row>
     <row r="75" spans="1:65">
       <c r="A75" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B75" t="s">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -14633,10 +14801,10 @@
     </row>
     <row r="76" spans="1:65">
       <c r="A76" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B76" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="H76">
         <v>1</v>
@@ -14815,10 +14983,10 @@
     </row>
     <row r="77" spans="1:65">
       <c r="A77" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B77" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="H77">
         <v>1</v>
@@ -14997,10 +15165,10 @@
     </row>
     <row r="78" spans="1:65">
       <c r="A78" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B78" t="s">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -15179,10 +15347,10 @@
     </row>
     <row r="79" spans="1:65">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B79" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -15361,10 +15529,10 @@
     </row>
     <row r="80" spans="1:65">
       <c r="A80" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B80" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -15543,10 +15711,10 @@
     </row>
     <row r="81" spans="1:65">
       <c r="A81" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B81" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -15725,10 +15893,10 @@
     </row>
     <row r="82" spans="1:65">
       <c r="A82" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B82" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -15907,10 +16075,10 @@
     </row>
     <row r="83" spans="1:65">
       <c r="A83" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B83" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -16089,10 +16257,10 @@
     </row>
     <row r="84" spans="1:65">
       <c r="A84" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B84" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -16271,10 +16439,10 @@
     </row>
     <row r="85" spans="1:65">
       <c r="A85" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B85" t="s">
-        <v>93</v>
+        <v>149</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -16453,10 +16621,10 @@
     </row>
     <row r="86" spans="1:65">
       <c r="A86" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B86" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -16635,10 +16803,10 @@
     </row>
     <row r="87" spans="1:65">
       <c r="A87" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B87" t="s">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="H87">
         <v>1</v>
@@ -16817,10 +16985,10 @@
     </row>
     <row r="88" spans="1:65">
       <c r="A88" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B88" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -16999,10 +17167,10 @@
     </row>
     <row r="89" spans="1:65">
       <c r="A89" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B89" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="H89">
         <v>1</v>
@@ -17181,10 +17349,10 @@
     </row>
     <row r="90" spans="1:65">
       <c r="A90" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B90" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="H90">
         <v>1</v>
@@ -17363,10 +17531,10 @@
     </row>
     <row r="91" spans="1:65">
       <c r="A91" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B91" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="H91">
         <v>1</v>
@@ -17545,10 +17713,10 @@
     </row>
     <row r="92" spans="1:65">
       <c r="A92" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B92" t="s">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -17727,10 +17895,10 @@
     </row>
     <row r="93" spans="1:65">
       <c r="A93" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B93" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -17909,10 +18077,10 @@
     </row>
     <row r="94" spans="1:65">
       <c r="A94" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B94" t="s">
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -18091,10 +18259,10 @@
     </row>
     <row r="95" spans="1:65">
       <c r="A95" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B95" t="s">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -18273,10 +18441,10 @@
     </row>
     <row r="96" spans="1:65">
       <c r="A96" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B96" t="s">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -18455,10 +18623,10 @@
     </row>
     <row r="97" spans="1:65">
       <c r="A97" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B97" t="s">
-        <v>105</v>
+        <v>161</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -18637,10 +18805,10 @@
     </row>
     <row r="98" spans="1:65">
       <c r="A98" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B98" t="s">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -18819,10 +18987,10 @@
     </row>
     <row r="99" spans="1:65">
       <c r="A99" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B99" t="s">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -19001,10 +19169,10 @@
     </row>
     <row r="100" spans="1:65">
       <c r="A100" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B100" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -19183,10 +19351,10 @@
     </row>
     <row r="101" spans="1:65">
       <c r="A101" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B101" t="s">
-        <v>109</v>
+        <v>165</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -19365,10 +19533,10 @@
     </row>
     <row r="102" spans="1:65">
       <c r="A102" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B102" t="s">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -19547,10 +19715,10 @@
     </row>
     <row r="103" spans="1:65">
       <c r="A103" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B103" t="s">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -19729,10 +19897,10 @@
     </row>
     <row r="104" spans="1:65">
       <c r="A104" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B104" t="s">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -19911,10 +20079,10 @@
     </row>
     <row r="105" spans="1:65">
       <c r="A105" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B105" t="s">
-        <v>113</v>
+        <v>169</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -20093,10 +20261,10 @@
     </row>
     <row r="106" spans="1:65">
       <c r="A106" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B106" t="s">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="H106">
         <v>1</v>
@@ -20275,10 +20443,10 @@
     </row>
     <row r="107" spans="1:65">
       <c r="A107" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B107" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="H107">
         <v>1</v>
@@ -20457,10 +20625,10 @@
     </row>
     <row r="108" spans="1:65">
       <c r="A108" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B108" t="s">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="H108">
         <v>1</v>
@@ -20639,10 +20807,10 @@
     </row>
     <row r="109" spans="1:65">
       <c r="A109" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B109" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
       <c r="H109">
         <v>1</v>
@@ -20821,10 +20989,10 @@
     </row>
     <row r="110" spans="1:65">
       <c r="A110" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B110" t="s">
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="H110">
         <v>1</v>
@@ -21003,10 +21171,10 @@
     </row>
     <row r="111" spans="1:65">
       <c r="A111" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B111" t="s">
-        <v>119</v>
+        <v>175</v>
       </c>
       <c r="H111">
         <v>1</v>
@@ -21185,10 +21353,10 @@
     </row>
     <row r="112" spans="1:65">
       <c r="A112" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B112" t="s">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="H112">
         <v>1</v>
@@ -21367,10 +21535,10 @@
     </row>
     <row r="113" spans="1:65">
       <c r="A113" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B113" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="H113">
         <v>1</v>
@@ -21549,10 +21717,10 @@
     </row>
     <row r="114" spans="1:65">
       <c r="A114" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B114" t="s">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="H114">
         <v>1</v>
@@ -21731,10 +21899,10 @@
     </row>
     <row r="115" spans="1:65">
       <c r="A115" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B115" t="s">
-        <v>123</v>
+        <v>179</v>
       </c>
       <c r="H115">
         <v>1</v>
@@ -21913,10 +22081,10 @@
     </row>
     <row r="116" spans="1:65">
       <c r="A116" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B116" t="s">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="H116">
         <v>1</v>
@@ -22095,10 +22263,10 @@
     </row>
     <row r="117" spans="1:65">
       <c r="A117" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B117" t="s">
-        <v>125</v>
+        <v>181</v>
       </c>
       <c r="H117">
         <v>1</v>
@@ -22277,10 +22445,10 @@
     </row>
     <row r="118" spans="1:65">
       <c r="A118" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B118" t="s">
-        <v>126</v>
+        <v>182</v>
       </c>
       <c r="H118">
         <v>1</v>
@@ -22459,10 +22627,10 @@
     </row>
     <row r="119" spans="1:65">
       <c r="A119" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B119" t="s">
-        <v>127</v>
+        <v>183</v>
       </c>
       <c r="H119">
         <v>1</v>
@@ -22641,10 +22809,10 @@
     </row>
     <row r="120" spans="1:65">
       <c r="A120" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B120" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="H120">
         <v>1</v>
@@ -22823,10 +22991,10 @@
     </row>
     <row r="121" spans="1:65">
       <c r="A121" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B121" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="H121">
         <v>1</v>
@@ -23005,10 +23173,10 @@
     </row>
     <row r="122" spans="1:65">
       <c r="A122" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B122" t="s">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="H122">
         <v>1</v>
@@ -23187,10 +23355,10 @@
     </row>
     <row r="123" spans="1:65">
       <c r="A123" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B123" t="s">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="H123">
         <v>1</v>
@@ -23369,10 +23537,10 @@
     </row>
     <row r="124" spans="1:65">
       <c r="A124" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B124" t="s">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="H124">
         <v>1</v>
@@ -23551,10 +23719,10 @@
     </row>
     <row r="125" spans="1:65">
       <c r="A125" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B125" t="s">
-        <v>133</v>
+        <v>189</v>
       </c>
       <c r="H125">
         <v>1</v>
@@ -23733,10 +23901,10 @@
     </row>
     <row r="126" spans="1:65">
       <c r="A126" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B126" t="s">
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="H126">
         <v>1</v>
@@ -23915,10 +24083,10 @@
     </row>
     <row r="127" spans="1:65">
       <c r="A127" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B127" t="s">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="H127">
         <v>1</v>
@@ -24097,10 +24265,10 @@
     </row>
     <row r="128" spans="1:65">
       <c r="A128" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B128" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="H128">
         <v>1</v>
@@ -24279,10 +24447,10 @@
     </row>
     <row r="129" spans="1:65">
       <c r="A129" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B129" t="s">
-        <v>137</v>
+        <v>193</v>
       </c>
       <c r="H129">
         <v>1</v>
@@ -24461,10 +24629,10 @@
     </row>
     <row r="130" spans="1:65">
       <c r="A130" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B130" t="s">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="H130">
         <v>1</v>
@@ -24643,10 +24811,10 @@
     </row>
     <row r="131" spans="1:65">
       <c r="A131" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B131" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="H131">
         <v>1</v>
@@ -24825,10 +24993,10 @@
     </row>
     <row r="132" spans="1:65">
       <c r="A132" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B132" t="s">
-        <v>140</v>
+        <v>196</v>
       </c>
       <c r="H132">
         <v>1</v>
@@ -25007,10 +25175,10 @@
     </row>
     <row r="133" spans="1:65">
       <c r="A133" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B133" t="s">
-        <v>141</v>
+        <v>197</v>
       </c>
       <c r="H133">
         <v>1</v>
@@ -25189,10 +25357,10 @@
     </row>
     <row r="134" spans="1:65">
       <c r="A134" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B134" t="s">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="H134">
         <v>1</v>
@@ -25371,10 +25539,10 @@
     </row>
     <row r="135" spans="1:65">
       <c r="A135" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B135" t="s">
-        <v>143</v>
+        <v>199</v>
       </c>
       <c r="H135">
         <v>1</v>
@@ -25553,10 +25721,10 @@
     </row>
     <row r="136" spans="1:65">
       <c r="A136" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B136" t="s">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="H136">
         <v>1</v>
@@ -25735,10 +25903,10 @@
     </row>
     <row r="137" spans="1:65">
       <c r="A137" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B137" t="s">
-        <v>145</v>
+        <v>201</v>
       </c>
       <c r="H137">
         <v>1</v>
@@ -25917,10 +26085,10 @@
     </row>
     <row r="138" spans="1:65">
       <c r="A138" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B138" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="H138">
         <v>1</v>
@@ -26099,10 +26267,10 @@
     </row>
     <row r="139" spans="1:65">
       <c r="A139" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B139" t="s">
-        <v>147</v>
+        <v>203</v>
       </c>
       <c r="H139">
         <v>1</v>
@@ -26281,10 +26449,10 @@
     </row>
     <row r="140" spans="1:65">
       <c r="A140" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B140" t="s">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="H140">
         <v>1</v>
@@ -26463,10 +26631,10 @@
     </row>
     <row r="141" spans="1:65">
       <c r="A141" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B141" t="s">
-        <v>149</v>
+        <v>205</v>
       </c>
       <c r="H141">
         <v>1</v>
@@ -26645,10 +26813,10 @@
     </row>
     <row r="142" spans="1:65">
       <c r="A142" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B142" t="s">
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="H142">
         <v>1</v>
@@ -26827,10 +26995,10 @@
     </row>
     <row r="143" spans="1:65">
       <c r="A143" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B143" t="s">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="H143">
         <v>1</v>
@@ -27009,10 +27177,10 @@
     </row>
     <row r="144" spans="1:65">
       <c r="A144" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B144" t="s">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="H144">
         <v>1</v>
@@ -27191,10 +27359,10 @@
     </row>
     <row r="145" spans="1:65">
       <c r="A145" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B145" t="s">
-        <v>153</v>
+        <v>209</v>
       </c>
       <c r="H145">
         <v>1</v>
@@ -27373,10 +27541,10 @@
     </row>
     <row r="146" spans="1:65">
       <c r="A146" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="H146">
         <v>1</v>
@@ -27555,10 +27723,10 @@
     </row>
     <row r="147" spans="1:65">
       <c r="A147" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B147" t="s">
-        <v>155</v>
+        <v>211</v>
       </c>
       <c r="H147">
         <v>1</v>
@@ -27737,10 +27905,10 @@
     </row>
     <row r="148" spans="1:65">
       <c r="A148" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B148" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
       <c r="H148">
         <v>1</v>
@@ -27919,10 +28087,10 @@
     </row>
     <row r="149" spans="1:65">
       <c r="A149" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B149" t="s">
-        <v>157</v>
+        <v>213</v>
       </c>
       <c r="H149">
         <v>1</v>
@@ -28101,10 +28269,10 @@
     </row>
     <row r="150" spans="1:65">
       <c r="A150" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B150" t="s">
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="H150">
         <v>1</v>
@@ -28283,10 +28451,10 @@
     </row>
     <row r="151" spans="1:65">
       <c r="A151" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B151" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="H151">
         <v>1</v>
@@ -28465,10 +28633,10 @@
     </row>
     <row r="152" spans="1:65">
       <c r="A152" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B152" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="H152">
         <v>1</v>
@@ -28647,10 +28815,10 @@
     </row>
     <row r="153" spans="1:65">
       <c r="A153" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B153" t="s">
-        <v>161</v>
+        <v>217</v>
       </c>
       <c r="H153">
         <v>1</v>
@@ -28829,10 +28997,10 @@
     </row>
     <row r="154" spans="1:65">
       <c r="A154" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B154" t="s">
-        <v>162</v>
+        <v>218</v>
       </c>
       <c r="H154">
         <v>1</v>
@@ -29011,10 +29179,10 @@
     </row>
     <row r="155" spans="1:65">
       <c r="A155" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B155" t="s">
-        <v>163</v>
+        <v>219</v>
       </c>
       <c r="H155">
         <v>1</v>
@@ -29193,10 +29361,10 @@
     </row>
     <row r="156" spans="1:65">
       <c r="A156" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B156" t="s">
-        <v>164</v>
+        <v>220</v>
       </c>
       <c r="H156">
         <v>1</v>
@@ -29375,10 +29543,10 @@
     </row>
     <row r="157" spans="1:65">
       <c r="A157" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B157" t="s">
-        <v>165</v>
+        <v>221</v>
       </c>
       <c r="H157">
         <v>1</v>
@@ -29557,10 +29725,10 @@
     </row>
     <row r="158" spans="1:65">
       <c r="A158" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B158" t="s">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="H158">
         <v>1</v>
@@ -29739,10 +29907,10 @@
     </row>
     <row r="159" spans="1:65">
       <c r="A159" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B159" t="s">
-        <v>167</v>
+        <v>223</v>
       </c>
       <c r="H159">
         <v>1</v>
@@ -29921,10 +30089,10 @@
     </row>
     <row r="160" spans="1:65">
       <c r="A160" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B160" t="s">
-        <v>168</v>
+        <v>224</v>
       </c>
       <c r="H160">
         <v>1</v>
@@ -30103,10 +30271,10 @@
     </row>
     <row r="161" spans="1:65">
       <c r="A161" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B161" t="s">
-        <v>169</v>
+        <v>225</v>
       </c>
       <c r="H161">
         <v>1</v>
@@ -30285,10 +30453,10 @@
     </row>
     <row r="162" spans="1:65">
       <c r="A162" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B162" t="s">
-        <v>170</v>
+        <v>226</v>
       </c>
       <c r="H162">
         <v>1</v>
@@ -30467,10 +30635,10 @@
     </row>
     <row r="163" spans="1:65">
       <c r="A163" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B163" t="s">
-        <v>171</v>
+        <v>227</v>
       </c>
       <c r="H163">
         <v>1</v>
@@ -30649,10 +30817,10 @@
     </row>
     <row r="164" spans="1:65">
       <c r="A164" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B164" t="s">
-        <v>172</v>
+        <v>228</v>
       </c>
       <c r="H164">
         <v>1</v>
@@ -30831,10 +30999,10 @@
     </row>
     <row r="165" spans="1:65">
       <c r="A165" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B165" t="s">
-        <v>173</v>
+        <v>229</v>
       </c>
       <c r="H165">
         <v>1</v>
@@ -31013,10 +31181,10 @@
     </row>
     <row r="166" spans="1:65">
       <c r="A166" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B166" t="s">
-        <v>174</v>
+        <v>230</v>
       </c>
       <c r="H166">
         <v>1</v>
@@ -31195,10 +31363,10 @@
     </row>
     <row r="167" spans="1:65">
       <c r="A167" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B167" t="s">
-        <v>175</v>
+        <v>231</v>
       </c>
       <c r="H167">
         <v>1</v>
@@ -31377,10 +31545,10 @@
     </row>
     <row r="168" spans="1:65">
       <c r="A168" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B168" t="s">
-        <v>176</v>
+        <v>232</v>
       </c>
       <c r="H168">
         <v>1</v>
@@ -31559,10 +31727,10 @@
     </row>
     <row r="169" spans="1:65">
       <c r="A169" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B169" t="s">
-        <v>177</v>
+        <v>233</v>
       </c>
       <c r="H169">
         <v>1</v>
@@ -31741,10 +31909,10 @@
     </row>
     <row r="170" spans="1:65">
       <c r="A170" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B170" t="s">
-        <v>178</v>
+        <v>234</v>
       </c>
       <c r="H170">
         <v>1</v>
@@ -31923,10 +32091,10 @@
     </row>
     <row r="171" spans="1:65">
       <c r="A171" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B171" t="s">
-        <v>179</v>
+        <v>235</v>
       </c>
       <c r="H171">
         <v>1</v>
@@ -32105,10 +32273,10 @@
     </row>
     <row r="172" spans="1:65">
       <c r="A172" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B172" t="s">
-        <v>180</v>
+        <v>236</v>
       </c>
       <c r="H172">
         <v>1</v>
@@ -32287,10 +32455,10 @@
     </row>
     <row r="173" spans="1:65">
       <c r="A173" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B173" t="s">
-        <v>181</v>
+        <v>237</v>
       </c>
       <c r="H173">
         <v>1</v>
@@ -32469,10 +32637,10 @@
     </row>
     <row r="174" spans="1:65">
       <c r="A174" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B174" t="s">
-        <v>182</v>
+        <v>238</v>
       </c>
       <c r="H174">
         <v>1</v>
@@ -32651,10 +32819,10 @@
     </row>
     <row r="175" spans="1:65">
       <c r="A175" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B175" t="s">
-        <v>183</v>
+        <v>239</v>
       </c>
       <c r="H175">
         <v>1</v>
@@ -32833,10 +33001,10 @@
     </row>
     <row r="176" spans="1:65">
       <c r="A176" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B176" t="s">
-        <v>184</v>
+        <v>240</v>
       </c>
       <c r="H176">
         <v>1</v>
@@ -33015,10 +33183,10 @@
     </row>
     <row r="177" spans="1:65">
       <c r="A177" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B177" t="s">
-        <v>185</v>
+        <v>241</v>
       </c>
       <c r="H177">
         <v>1</v>
@@ -33197,10 +33365,10 @@
     </row>
     <row r="178" spans="1:65">
       <c r="A178" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B178" t="s">
-        <v>186</v>
+        <v>242</v>
       </c>
       <c r="H178">
         <v>1</v>
@@ -33379,10 +33547,10 @@
     </row>
     <row r="179" spans="1:65">
       <c r="A179" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B179" t="s">
-        <v>187</v>
+        <v>243</v>
       </c>
       <c r="H179">
         <v>1</v>
@@ -33561,10 +33729,10 @@
     </row>
     <row r="180" spans="1:65">
       <c r="A180" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B180" t="s">
-        <v>188</v>
+        <v>244</v>
       </c>
       <c r="H180">
         <v>1</v>
@@ -33743,10 +33911,10 @@
     </row>
     <row r="181" spans="1:65">
       <c r="A181" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B181" t="s">
-        <v>189</v>
+        <v>245</v>
       </c>
       <c r="H181">
         <v>1</v>
@@ -33925,10 +34093,10 @@
     </row>
     <row r="182" spans="1:65">
       <c r="A182" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B182" t="s">
-        <v>190</v>
+        <v>246</v>
       </c>
       <c r="H182">
         <v>1</v>
@@ -34107,10 +34275,10 @@
     </row>
     <row r="183" spans="1:65">
       <c r="A183" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B183" t="s">
-        <v>191</v>
+        <v>247</v>
       </c>
       <c r="H183">
         <v>1</v>
@@ -34289,10 +34457,10 @@
     </row>
     <row r="184" spans="1:65">
       <c r="A184" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B184" t="s">
-        <v>192</v>
+        <v>248</v>
       </c>
       <c r="H184">
         <v>1</v>
@@ -34471,10 +34639,10 @@
     </row>
     <row r="185" spans="1:65">
       <c r="A185" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B185" t="s">
-        <v>193</v>
+        <v>249</v>
       </c>
       <c r="H185">
         <v>1</v>
@@ -34653,10 +34821,10 @@
     </row>
     <row r="186" spans="1:65">
       <c r="A186" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B186" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="H186">
         <v>1</v>
@@ -34835,10 +35003,10 @@
     </row>
     <row r="187" spans="1:65">
       <c r="A187" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B187" t="s">
-        <v>195</v>
+        <v>251</v>
       </c>
       <c r="H187">
         <v>1</v>
@@ -35053,181 +35221,181 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2</v>
-      </c>
-      <c r="M1" s="1">
-        <v>3</v>
-      </c>
-      <c r="N1" s="1">
-        <v>4</v>
-      </c>
-      <c r="O1" s="1">
-        <v>5</v>
-      </c>
-      <c r="P1" s="1">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>7</v>
-      </c>
-      <c r="R1" s="1">
-        <v>8</v>
-      </c>
-      <c r="S1" s="1">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="1">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="1">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="1">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="1">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="1">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="1">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="1">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="1">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="1">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="1">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="1">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="1">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" s="1">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="1">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AV1" s="1">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="1">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="1">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AY1" s="1">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="1">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BA1" s="1">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BB1" s="1">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BC1" s="1">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BD1" s="1">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BE1" s="1">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BF1" s="1">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BG1" s="1">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BH1" s="1">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BI1" s="1">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BJ1" s="1">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BK1" s="1">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BL1" s="1">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BM1" s="1">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:65">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="H2">
         <v>1.5</v>
@@ -35406,10 +35574,10 @@
     </row>
     <row r="3" spans="1:65">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="H3">
         <v>1.5</v>
@@ -35588,10 +35756,10 @@
     </row>
     <row r="4" spans="1:65">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="H4">
         <v>1.5</v>
@@ -35770,10 +35938,10 @@
     </row>
     <row r="5" spans="1:65">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="H5">
         <v>1.5</v>
@@ -35952,10 +36120,10 @@
     </row>
     <row r="6" spans="1:65">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="H6">
         <v>1.5</v>
@@ -36134,10 +36302,10 @@
     </row>
     <row r="7" spans="1:65">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="H7">
         <v>1.5</v>
@@ -36316,10 +36484,10 @@
     </row>
     <row r="8" spans="1:65">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="H8">
         <v>1.5</v>
@@ -36498,10 +36666,10 @@
     </row>
     <row r="9" spans="1:65">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="H9">
         <v>1.5</v>
@@ -36680,10 +36848,10 @@
     </row>
     <row r="10" spans="1:65">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="H10">
         <v>1.5</v>
@@ -36862,10 +37030,10 @@
     </row>
     <row r="11" spans="1:65">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="H11">
         <v>1.5</v>
@@ -37044,10 +37212,10 @@
     </row>
     <row r="12" spans="1:65">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="H12">
         <v>1.5</v>
@@ -37226,10 +37394,10 @@
     </row>
     <row r="13" spans="1:65">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="H13">
         <v>1.5</v>
@@ -37408,10 +37576,10 @@
     </row>
     <row r="14" spans="1:65">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="H14">
         <v>1.5</v>
@@ -37590,10 +37758,10 @@
     </row>
     <row r="15" spans="1:65">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="H15">
         <v>1.5</v>
@@ -37772,10 +37940,10 @@
     </row>
     <row r="16" spans="1:65">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="H16">
         <v>1.5</v>
@@ -37954,10 +38122,10 @@
     </row>
     <row r="17" spans="1:65">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="H17">
         <v>1.5</v>
@@ -38136,10 +38304,10 @@
     </row>
     <row r="18" spans="1:65">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="H18">
         <v>1.5</v>
@@ -38318,10 +38486,10 @@
     </row>
     <row r="19" spans="1:65">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="H19">
         <v>1.5</v>
@@ -38500,10 +38668,10 @@
     </row>
     <row r="20" spans="1:65">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="H20">
         <v>1.5</v>
@@ -38682,10 +38850,10 @@
     </row>
     <row r="21" spans="1:65">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="H21">
         <v>1.5</v>
@@ -38864,10 +39032,10 @@
     </row>
     <row r="22" spans="1:65">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -39046,10 +39214,10 @@
     </row>
     <row r="23" spans="1:65">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -39228,10 +39396,10 @@
     </row>
     <row r="24" spans="1:65">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -39410,10 +39578,10 @@
     </row>
     <row r="25" spans="1:65">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -39592,10 +39760,10 @@
     </row>
     <row r="26" spans="1:65">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -39774,10 +39942,10 @@
     </row>
     <row r="27" spans="1:65">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -39956,10 +40124,10 @@
     </row>
     <row r="28" spans="1:65">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>123</v>
+        <v>179</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -40138,10 +40306,10 @@
     </row>
     <row r="29" spans="1:65">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -40320,10 +40488,10 @@
     </row>
     <row r="30" spans="1:65">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>183</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -40502,10 +40670,10 @@
     </row>
     <row r="31" spans="1:65">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -40684,10 +40852,10 @@
     </row>
     <row r="32" spans="1:65">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -40866,10 +41034,10 @@
     </row>
     <row r="33" spans="1:65">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B33" t="s">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -41048,10 +41216,10 @@
     </row>
     <row r="34" spans="1:65">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -41230,10 +41398,10 @@
     </row>
     <row r="35" spans="1:65">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -41412,10 +41580,10 @@
     </row>
     <row r="36" spans="1:65">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>189</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -41594,10 +41762,10 @@
     </row>
     <row r="37" spans="1:65">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -41812,181 +41980,181 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2</v>
-      </c>
-      <c r="M1" s="1">
-        <v>3</v>
-      </c>
-      <c r="N1" s="1">
-        <v>4</v>
-      </c>
-      <c r="O1" s="1">
-        <v>5</v>
-      </c>
-      <c r="P1" s="1">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>7</v>
-      </c>
-      <c r="R1" s="1">
-        <v>8</v>
-      </c>
-      <c r="S1" s="1">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="1">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="1">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="1">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="1">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="1">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="1">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="1">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="1">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="1">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="1">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="1">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="1">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" s="1">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="1">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AV1" s="1">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="1">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="1">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AY1" s="1">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="1">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BA1" s="1">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BB1" s="1">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BC1" s="1">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BD1" s="1">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BE1" s="1">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BF1" s="1">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BG1" s="1">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BH1" s="1">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BI1" s="1">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BJ1" s="1">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BK1" s="1">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BL1" s="1">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BM1" s="1">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:65">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="H2">
         <v>1.5</v>
@@ -42165,10 +42333,10 @@
     </row>
     <row r="3" spans="1:65">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="H3">
         <v>1.5</v>
@@ -42347,10 +42515,10 @@
     </row>
     <row r="4" spans="1:65">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="H4">
         <v>1.5</v>
@@ -42529,10 +42697,10 @@
     </row>
     <row r="5" spans="1:65">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="H5">
         <v>1.5</v>
@@ -42711,10 +42879,10 @@
     </row>
     <row r="6" spans="1:65">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="H6">
         <v>1.5</v>
@@ -42893,10 +43061,10 @@
     </row>
     <row r="7" spans="1:65">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="H7">
         <v>1.5</v>
@@ -43075,10 +43243,10 @@
     </row>
     <row r="8" spans="1:65">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="H8">
         <v>1.5</v>
@@ -43257,10 +43425,10 @@
     </row>
     <row r="9" spans="1:65">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="H9">
         <v>1.5</v>
@@ -43439,10 +43607,10 @@
     </row>
     <row r="10" spans="1:65">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="H10">
         <v>1.5</v>
@@ -43621,10 +43789,10 @@
     </row>
     <row r="11" spans="1:65">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="H11">
         <v>1.5</v>
@@ -43803,10 +43971,10 @@
     </row>
     <row r="12" spans="1:65">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="H12">
         <v>1.5</v>
@@ -43985,10 +44153,10 @@
     </row>
     <row r="13" spans="1:65">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="H13">
         <v>1.5</v>
@@ -44167,10 +44335,10 @@
     </row>
     <row r="14" spans="1:65">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="H14">
         <v>1.5</v>
@@ -44349,10 +44517,10 @@
     </row>
     <row r="15" spans="1:65">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="H15">
         <v>1.5</v>
@@ -44531,10 +44699,10 @@
     </row>
     <row r="16" spans="1:65">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="H16">
         <v>1.5</v>
@@ -44713,10 +44881,10 @@
     </row>
     <row r="17" spans="1:65">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="H17">
         <v>1.5</v>
@@ -44895,10 +45063,10 @@
     </row>
     <row r="18" spans="1:65">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="H18">
         <v>1.5</v>
@@ -45077,10 +45245,10 @@
     </row>
     <row r="19" spans="1:65">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="H19">
         <v>1.5</v>
@@ -45259,10 +45427,10 @@
     </row>
     <row r="20" spans="1:65">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="H20">
         <v>1.5</v>
@@ -45441,10 +45609,10 @@
     </row>
     <row r="21" spans="1:65">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="H21">
         <v>1.5</v>
@@ -45623,10 +45791,10 @@
     </row>
     <row r="22" spans="1:65">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -45841,181 +46009,181 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2</v>
-      </c>
-      <c r="M1" s="1">
-        <v>3</v>
-      </c>
-      <c r="N1" s="1">
-        <v>4</v>
-      </c>
-      <c r="O1" s="1">
-        <v>5</v>
-      </c>
-      <c r="P1" s="1">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>7</v>
-      </c>
-      <c r="R1" s="1">
-        <v>8</v>
-      </c>
-      <c r="S1" s="1">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="1">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="1">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="1">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="1">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="1">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="1">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="1">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="1">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="1">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="1">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="1">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="1">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" s="1">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="1">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AV1" s="1">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="1">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="1">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AY1" s="1">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="1">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BA1" s="1">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BB1" s="1">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BC1" s="1">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BD1" s="1">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BE1" s="1">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BF1" s="1">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BG1" s="1">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BH1" s="1">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BI1" s="1">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BJ1" s="1">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BK1" s="1">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BL1" s="1">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BM1" s="1">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:65">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="H2">
         <v>1.5</v>
@@ -46194,10 +46362,10 @@
     </row>
     <row r="3" spans="1:65">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="H3">
         <v>1.5</v>
@@ -46376,10 +46544,10 @@
     </row>
     <row r="4" spans="1:65">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="H4">
         <v>1.5</v>
@@ -46558,10 +46726,10 @@
     </row>
     <row r="5" spans="1:65">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="H5">
         <v>1.5</v>
@@ -46740,10 +46908,10 @@
     </row>
     <row r="6" spans="1:65">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="H6">
         <v>1.5</v>
@@ -46922,10 +47090,10 @@
     </row>
     <row r="7" spans="1:65">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="H7">
         <v>1.5</v>
@@ -47104,10 +47272,10 @@
     </row>
     <row r="8" spans="1:65">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="H8">
         <v>1.5</v>
@@ -47286,10 +47454,10 @@
     </row>
     <row r="9" spans="1:65">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="H9">
         <v>1.5</v>
@@ -47468,10 +47636,10 @@
     </row>
     <row r="10" spans="1:65">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="H10">
         <v>1.5</v>
@@ -47650,10 +47818,10 @@
     </row>
     <row r="11" spans="1:65">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="H11">
         <v>1.5</v>
@@ -47832,10 +48000,10 @@
     </row>
     <row r="12" spans="1:65">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="H12">
         <v>1.5</v>
@@ -48014,10 +48182,10 @@
     </row>
     <row r="13" spans="1:65">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="H13">
         <v>1.5</v>
@@ -48196,10 +48364,10 @@
     </row>
     <row r="14" spans="1:65">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="H14">
         <v>1.5</v>
@@ -48378,10 +48546,10 @@
     </row>
     <row r="15" spans="1:65">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="H15">
         <v>1.5</v>
@@ -48560,10 +48728,10 @@
     </row>
     <row r="16" spans="1:65">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="H16">
         <v>1.5</v>
@@ -48742,10 +48910,10 @@
     </row>
     <row r="17" spans="1:65">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="H17">
         <v>1.5</v>
@@ -48924,10 +49092,10 @@
     </row>
     <row r="18" spans="1:65">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="H18">
         <v>1.5</v>
@@ -49106,10 +49274,10 @@
     </row>
     <row r="19" spans="1:65">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="H19">
         <v>1.5</v>
@@ -49288,10 +49456,10 @@
     </row>
     <row r="20" spans="1:65">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="H20">
         <v>1.5</v>
@@ -49470,10 +49638,10 @@
     </row>
     <row r="21" spans="1:65">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="H21">
         <v>1.5</v>
@@ -49652,10 +49820,10 @@
     </row>
     <row r="22" spans="1:65">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -49834,10 +50002,10 @@
     </row>
     <row r="23" spans="1:65">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -50016,10 +50184,10 @@
     </row>
     <row r="24" spans="1:65">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -50198,10 +50366,10 @@
     </row>
     <row r="25" spans="1:65">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -50380,10 +50548,10 @@
     </row>
     <row r="26" spans="1:65">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -50562,10 +50730,10 @@
     </row>
     <row r="27" spans="1:65">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -50744,10 +50912,10 @@
     </row>
     <row r="28" spans="1:65">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>123</v>
+        <v>179</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -50926,10 +51094,10 @@
     </row>
     <row r="29" spans="1:65">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -51108,10 +51276,10 @@
     </row>
     <row r="30" spans="1:65">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>183</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -51290,10 +51458,10 @@
     </row>
     <row r="31" spans="1:65">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -51472,10 +51640,10 @@
     </row>
     <row r="32" spans="1:65">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -51654,10 +51822,10 @@
     </row>
     <row r="33" spans="1:65">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B33" t="s">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -51836,10 +52004,10 @@
     </row>
     <row r="34" spans="1:65">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -52018,10 +52186,10 @@
     </row>
     <row r="35" spans="1:65">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -52200,10 +52368,10 @@
     </row>
     <row r="36" spans="1:65">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>189</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -52382,10 +52550,10 @@
     </row>
     <row r="37" spans="1:65">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -52600,181 +52768,181 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2</v>
-      </c>
-      <c r="M1" s="1">
-        <v>3</v>
-      </c>
-      <c r="N1" s="1">
-        <v>4</v>
-      </c>
-      <c r="O1" s="1">
-        <v>5</v>
-      </c>
-      <c r="P1" s="1">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>7</v>
-      </c>
-      <c r="R1" s="1">
-        <v>8</v>
-      </c>
-      <c r="S1" s="1">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="1">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="1">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="1">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="1">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="1">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="1">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="1">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="1">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="1">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="1">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="1">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="1">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" s="1">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="1">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AV1" s="1">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="1">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="1">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AY1" s="1">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="1">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BA1" s="1">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BB1" s="1">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BC1" s="1">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BD1" s="1">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BE1" s="1">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BF1" s="1">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BG1" s="1">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BH1" s="1">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BI1" s="1">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BJ1" s="1">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BK1" s="1">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BL1" s="1">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BM1" s="1">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:65">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="H2">
         <v>1.5</v>
@@ -52953,10 +53121,10 @@
     </row>
     <row r="3" spans="1:65">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="H3">
         <v>1.5</v>
@@ -53135,10 +53303,10 @@
     </row>
     <row r="4" spans="1:65">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="H4">
         <v>1.5</v>
@@ -53317,10 +53485,10 @@
     </row>
     <row r="5" spans="1:65">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="H5">
         <v>1.5</v>
@@ -53499,10 +53667,10 @@
     </row>
     <row r="6" spans="1:65">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="H6">
         <v>1.5</v>
@@ -53681,10 +53849,10 @@
     </row>
     <row r="7" spans="1:65">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="H7">
         <v>1.5</v>
@@ -53863,10 +54031,10 @@
     </row>
     <row r="8" spans="1:65">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="H8">
         <v>1.5</v>
@@ -54045,10 +54213,10 @@
     </row>
     <row r="9" spans="1:65">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="H9">
         <v>1.5</v>
@@ -54227,10 +54395,10 @@
     </row>
     <row r="10" spans="1:65">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="H10">
         <v>1.5</v>
@@ -54409,10 +54577,10 @@
     </row>
     <row r="11" spans="1:65">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="H11">
         <v>1.5</v>
@@ -54591,10 +54759,10 @@
     </row>
     <row r="12" spans="1:65">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="H12">
         <v>1.5</v>
@@ -54773,10 +54941,10 @@
     </row>
     <row r="13" spans="1:65">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="H13">
         <v>1.5</v>
@@ -54955,10 +55123,10 @@
     </row>
     <row r="14" spans="1:65">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="H14">
         <v>1.5</v>
@@ -55137,10 +55305,10 @@
     </row>
     <row r="15" spans="1:65">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="H15">
         <v>1.5</v>
@@ -55319,10 +55487,10 @@
     </row>
     <row r="16" spans="1:65">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="H16">
         <v>1.5</v>
@@ -55501,10 +55669,10 @@
     </row>
     <row r="17" spans="1:65">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="H17">
         <v>1.5</v>
@@ -55683,10 +55851,10 @@
     </row>
     <row r="18" spans="1:65">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="H18">
         <v>1.5</v>
@@ -55865,10 +56033,10 @@
     </row>
     <row r="19" spans="1:65">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="H19">
         <v>1.5</v>
@@ -56047,10 +56215,10 @@
     </row>
     <row r="20" spans="1:65">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="H20">
         <v>1.5</v>
@@ -56229,10 +56397,10 @@
     </row>
     <row r="21" spans="1:65">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="H21">
         <v>1.5</v>
@@ -56411,10 +56579,10 @@
     </row>
     <row r="22" spans="1:65">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="H22">
         <v>1</v>

--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ip_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ip_calibrated.xlsx
@@ -9,20 +9,22 @@
   <sheets>
     <sheet name="strategy_id-0" sheetId="1" r:id="rId1"/>
     <sheet name="strategy_id-6004" sheetId="2" r:id="rId2"/>
-    <sheet name="strategy_id-6007" sheetId="3" r:id="rId3"/>
-    <sheet name="strategy_id-6008" sheetId="4" r:id="rId4"/>
+    <sheet name="strategy_id-6008" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="252">
   <si>
     <t>subsector</t>
   </si>
   <si>
     <t>variable</t>
+  </si>
+  <si>
+    <t>variable_trajectory_group</t>
   </si>
   <si>
     <t>normalize_group</t>
@@ -32,9 +34,6 @@
   </si>
   <si>
     <t>uniform_scaling_q</t>
-  </si>
-  <si>
-    <t>variable_trajectory_group</t>
   </si>
   <si>
     <t>variable_trajectory_group_trajectory_type</t>
@@ -1701,11 +1700,14 @@
       <c r="B4" t="s">
         <v>68</v>
       </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
       <c r="H4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1883,11 +1885,14 @@
       <c r="B5" t="s">
         <v>69</v>
       </c>
+      <c r="C5">
+        <v>16</v>
+      </c>
       <c r="H5">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -2065,11 +2070,14 @@
       <c r="B6" t="s">
         <v>70</v>
       </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
       <c r="H6">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -2247,11 +2255,14 @@
       <c r="B7" t="s">
         <v>71</v>
       </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
       <c r="H7">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -2429,11 +2440,14 @@
       <c r="B8" t="s">
         <v>72</v>
       </c>
+      <c r="C8">
+        <v>16</v>
+      </c>
       <c r="H8">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -2611,11 +2625,14 @@
       <c r="B9" t="s">
         <v>73</v>
       </c>
+      <c r="C9">
+        <v>16</v>
+      </c>
       <c r="H9">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -2793,11 +2810,14 @@
       <c r="B10" t="s">
         <v>74</v>
       </c>
+      <c r="C10">
+        <v>16</v>
+      </c>
       <c r="H10">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -2975,11 +2995,14 @@
       <c r="B11" t="s">
         <v>75</v>
       </c>
+      <c r="C11">
+        <v>16</v>
+      </c>
       <c r="H11">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -3157,11 +3180,14 @@
       <c r="B12" t="s">
         <v>76</v>
       </c>
+      <c r="C12">
+        <v>16</v>
+      </c>
       <c r="H12">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -3339,11 +3365,14 @@
       <c r="B13" t="s">
         <v>77</v>
       </c>
+      <c r="C13">
+        <v>16</v>
+      </c>
       <c r="H13">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -3521,11 +3550,14 @@
       <c r="B14" t="s">
         <v>78</v>
       </c>
+      <c r="C14">
+        <v>16</v>
+      </c>
       <c r="H14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -3703,11 +3735,14 @@
       <c r="B15" t="s">
         <v>79</v>
       </c>
+      <c r="C15">
+        <v>16</v>
+      </c>
       <c r="H15">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -3885,11 +3920,14 @@
       <c r="B16" t="s">
         <v>80</v>
       </c>
+      <c r="C16">
+        <v>16</v>
+      </c>
       <c r="H16">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -4067,11 +4105,14 @@
       <c r="B17" t="s">
         <v>81</v>
       </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
       <c r="H17">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -4249,11 +4290,14 @@
       <c r="B18" t="s">
         <v>82</v>
       </c>
+      <c r="C18">
+        <v>16</v>
+      </c>
       <c r="H18">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -4431,11 +4475,14 @@
       <c r="B19" t="s">
         <v>83</v>
       </c>
+      <c r="C19">
+        <v>16</v>
+      </c>
       <c r="H19">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -4613,11 +4660,14 @@
       <c r="B20" t="s">
         <v>84</v>
       </c>
+      <c r="C20">
+        <v>16</v>
+      </c>
       <c r="H20">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -4795,11 +4845,14 @@
       <c r="B21" t="s">
         <v>85</v>
       </c>
+      <c r="C21">
+        <v>16</v>
+      </c>
       <c r="H21">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -4977,11 +5030,14 @@
       <c r="B22" t="s">
         <v>86</v>
       </c>
+      <c r="C22">
+        <v>16</v>
+      </c>
       <c r="H22">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -5159,11 +5215,14 @@
       <c r="B23" t="s">
         <v>87</v>
       </c>
+      <c r="C23">
+        <v>16</v>
+      </c>
       <c r="H23">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -8981,6 +9040,9 @@
       <c r="B44" t="s">
         <v>108</v>
       </c>
+      <c r="C44">
+        <v>18</v>
+      </c>
       <c r="H44">
         <v>1</v>
       </c>
@@ -9891,6 +9953,9 @@
       <c r="B49" t="s">
         <v>113</v>
       </c>
+      <c r="C49">
+        <v>18</v>
+      </c>
       <c r="H49">
         <v>1</v>
       </c>
@@ -16989,6 +17054,9 @@
       <c r="B88" t="s">
         <v>152</v>
       </c>
+      <c r="C88">
+        <v>17</v>
+      </c>
       <c r="H88">
         <v>1</v>
       </c>
@@ -17171,6 +17239,9 @@
       <c r="B89" t="s">
         <v>153</v>
       </c>
+      <c r="C89">
+        <v>17</v>
+      </c>
       <c r="H89">
         <v>1</v>
       </c>
@@ -17353,6 +17424,9 @@
       <c r="B90" t="s">
         <v>154</v>
       </c>
+      <c r="C90">
+        <v>17</v>
+      </c>
       <c r="H90">
         <v>1</v>
       </c>
@@ -18627,11 +18701,14 @@
       <c r="B97" t="s">
         <v>161</v>
       </c>
+      <c r="C97">
+        <v>63</v>
+      </c>
       <c r="H97">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I97">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -18809,11 +18886,14 @@
       <c r="B98" t="s">
         <v>162</v>
       </c>
+      <c r="C98">
+        <v>63</v>
+      </c>
       <c r="H98">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I98">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J98">
         <v>-5.143222222222196</v>
@@ -18991,11 +19071,14 @@
       <c r="B99" t="s">
         <v>163</v>
       </c>
+      <c r="C99">
+        <v>63</v>
+      </c>
       <c r="H99">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I99">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J99">
         <v>2.927037037037025</v>
@@ -19173,11 +19256,14 @@
       <c r="B100" t="s">
         <v>164</v>
       </c>
+      <c r="C100">
+        <v>63</v>
+      </c>
       <c r="H100">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I100">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J100">
         <v>2.947944444444434</v>
@@ -19355,11 +19441,14 @@
       <c r="B101" t="s">
         <v>165</v>
       </c>
+      <c r="C101">
+        <v>63</v>
+      </c>
       <c r="H101">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I101">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J101">
         <v>2.94794444444443</v>
@@ -19537,11 +19626,14 @@
       <c r="B102" t="s">
         <v>166</v>
       </c>
+      <c r="C102">
+        <v>63</v>
+      </c>
       <c r="H102">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I102">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J102">
         <v>-1.77712962962962</v>
@@ -19719,11 +19811,14 @@
       <c r="B103" t="s">
         <v>167</v>
       </c>
+      <c r="C103">
+        <v>63</v>
+      </c>
       <c r="H103">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I103">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J103">
         <v>2.927037037037025</v>
@@ -19901,11 +19996,14 @@
       <c r="B104" t="s">
         <v>168</v>
       </c>
+      <c r="C104">
+        <v>63</v>
+      </c>
       <c r="H104">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I104">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J104">
         <v>2.048925925925917</v>
@@ -20083,11 +20181,14 @@
       <c r="B105" t="s">
         <v>169</v>
       </c>
+      <c r="C105">
+        <v>63</v>
+      </c>
       <c r="H105">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I105">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J105">
         <v>2.92703703703702</v>
@@ -20265,11 +20366,14 @@
       <c r="B106" t="s">
         <v>170</v>
       </c>
+      <c r="C106">
+        <v>64</v>
+      </c>
       <c r="H106">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I106">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J106">
         <v>0.01</v>
@@ -20447,11 +20551,14 @@
       <c r="B107" t="s">
         <v>171</v>
       </c>
+      <c r="C107">
+        <v>64</v>
+      </c>
       <c r="H107">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I107">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J107">
         <v>0.01</v>
@@ -20629,11 +20736,14 @@
       <c r="B108" t="s">
         <v>172</v>
       </c>
+      <c r="C108">
+        <v>64</v>
+      </c>
       <c r="H108">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I108">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J108">
         <v>0.01</v>
@@ -20811,11 +20921,14 @@
       <c r="B109" t="s">
         <v>173</v>
       </c>
+      <c r="C109">
+        <v>64</v>
+      </c>
       <c r="H109">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I109">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J109">
         <v>0.01</v>
@@ -20993,11 +21106,14 @@
       <c r="B110" t="s">
         <v>174</v>
       </c>
+      <c r="C110">
+        <v>63</v>
+      </c>
       <c r="H110">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I110">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J110">
         <v>0.4390555555555514</v>
@@ -21175,11 +21291,14 @@
       <c r="B111" t="s">
         <v>175</v>
       </c>
+      <c r="C111">
+        <v>63</v>
+      </c>
       <c r="H111">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I111">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J111">
         <v>0.4390555555555514</v>
@@ -21357,11 +21476,14 @@
       <c r="B112" t="s">
         <v>176</v>
       </c>
+      <c r="C112">
+        <v>63</v>
+      </c>
       <c r="H112">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I112">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J112">
         <v>2.048925925925917</v>
@@ -21721,6 +21843,9 @@
       <c r="B114" t="s">
         <v>178</v>
       </c>
+      <c r="C114">
+        <v>15</v>
+      </c>
       <c r="H114">
         <v>1</v>
       </c>
@@ -21903,6 +22028,9 @@
       <c r="B115" t="s">
         <v>179</v>
       </c>
+      <c r="C115">
+        <v>30</v>
+      </c>
       <c r="H115">
         <v>1</v>
       </c>
@@ -22085,6 +22213,9 @@
       <c r="B116" t="s">
         <v>180</v>
       </c>
+      <c r="C116">
+        <v>30</v>
+      </c>
       <c r="H116">
         <v>1</v>
       </c>
@@ -22631,6 +22762,9 @@
       <c r="B119" t="s">
         <v>183</v>
       </c>
+      <c r="C119">
+        <v>30</v>
+      </c>
       <c r="H119">
         <v>1</v>
       </c>
@@ -22812,6 +22946,9 @@
       </c>
       <c r="B120" t="s">
         <v>184</v>
+      </c>
+      <c r="C120">
+        <v>30</v>
       </c>
       <c r="H120">
         <v>1</v>
@@ -35396,11 +35533,14 @@
       <c r="B2" t="s">
         <v>68</v>
       </c>
+      <c r="C2">
+        <v>16</v>
+      </c>
       <c r="H2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -35578,11 +35718,14 @@
       <c r="B3" t="s">
         <v>69</v>
       </c>
+      <c r="C3">
+        <v>16</v>
+      </c>
       <c r="H3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -35760,11 +35903,14 @@
       <c r="B4" t="s">
         <v>70</v>
       </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
       <c r="H4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -35942,11 +36088,14 @@
       <c r="B5" t="s">
         <v>71</v>
       </c>
+      <c r="C5">
+        <v>16</v>
+      </c>
       <c r="H5">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -36124,11 +36273,14 @@
       <c r="B6" t="s">
         <v>72</v>
       </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
       <c r="H6">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -36306,11 +36458,14 @@
       <c r="B7" t="s">
         <v>73</v>
       </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
       <c r="H7">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -36488,11 +36643,14 @@
       <c r="B8" t="s">
         <v>74</v>
       </c>
+      <c r="C8">
+        <v>16</v>
+      </c>
       <c r="H8">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -36670,11 +36828,14 @@
       <c r="B9" t="s">
         <v>75</v>
       </c>
+      <c r="C9">
+        <v>16</v>
+      </c>
       <c r="H9">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -36852,11 +37013,14 @@
       <c r="B10" t="s">
         <v>76</v>
       </c>
+      <c r="C10">
+        <v>16</v>
+      </c>
       <c r="H10">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -37034,11 +37198,14 @@
       <c r="B11" t="s">
         <v>77</v>
       </c>
+      <c r="C11">
+        <v>16</v>
+      </c>
       <c r="H11">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -37216,11 +37383,14 @@
       <c r="B12" t="s">
         <v>78</v>
       </c>
+      <c r="C12">
+        <v>16</v>
+      </c>
       <c r="H12">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -37398,11 +37568,14 @@
       <c r="B13" t="s">
         <v>79</v>
       </c>
+      <c r="C13">
+        <v>16</v>
+      </c>
       <c r="H13">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -37580,11 +37753,14 @@
       <c r="B14" t="s">
         <v>80</v>
       </c>
+      <c r="C14">
+        <v>16</v>
+      </c>
       <c r="H14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -37762,11 +37938,14 @@
       <c r="B15" t="s">
         <v>81</v>
       </c>
+      <c r="C15">
+        <v>16</v>
+      </c>
       <c r="H15">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -37944,11 +38123,14 @@
       <c r="B16" t="s">
         <v>82</v>
       </c>
+      <c r="C16">
+        <v>16</v>
+      </c>
       <c r="H16">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -38126,11 +38308,14 @@
       <c r="B17" t="s">
         <v>83</v>
       </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
       <c r="H17">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -38308,11 +38493,14 @@
       <c r="B18" t="s">
         <v>84</v>
       </c>
+      <c r="C18">
+        <v>16</v>
+      </c>
       <c r="H18">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -38490,11 +38678,14 @@
       <c r="B19" t="s">
         <v>85</v>
       </c>
+      <c r="C19">
+        <v>16</v>
+      </c>
       <c r="H19">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -38672,11 +38863,14 @@
       <c r="B20" t="s">
         <v>86</v>
       </c>
+      <c r="C20">
+        <v>16</v>
+      </c>
       <c r="H20">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -38854,11 +39048,14 @@
       <c r="B21" t="s">
         <v>87</v>
       </c>
+      <c r="C21">
+        <v>16</v>
+      </c>
       <c r="H21">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -39036,6 +39233,9 @@
       <c r="B22" t="s">
         <v>108</v>
       </c>
+      <c r="C22">
+        <v>18</v>
+      </c>
       <c r="H22">
         <v>1</v>
       </c>
@@ -39218,6 +39418,9 @@
       <c r="B23" t="s">
         <v>113</v>
       </c>
+      <c r="C23">
+        <v>18</v>
+      </c>
       <c r="H23">
         <v>1</v>
       </c>
@@ -39400,6 +39603,9 @@
       <c r="B24" t="s">
         <v>152</v>
       </c>
+      <c r="C24">
+        <v>17</v>
+      </c>
       <c r="H24">
         <v>1</v>
       </c>
@@ -39582,6 +39788,9 @@
       <c r="B25" t="s">
         <v>153</v>
       </c>
+      <c r="C25">
+        <v>17</v>
+      </c>
       <c r="H25">
         <v>1</v>
       </c>
@@ -39764,6 +39973,9 @@
       <c r="B26" t="s">
         <v>154</v>
       </c>
+      <c r="C26">
+        <v>17</v>
+      </c>
       <c r="H26">
         <v>1</v>
       </c>
@@ -39946,6 +40158,9 @@
       <c r="B27" t="s">
         <v>178</v>
       </c>
+      <c r="C27">
+        <v>15</v>
+      </c>
       <c r="H27">
         <v>1</v>
       </c>
@@ -40128,6 +40343,9 @@
       <c r="B28" t="s">
         <v>179</v>
       </c>
+      <c r="C28">
+        <v>30</v>
+      </c>
       <c r="H28">
         <v>1</v>
       </c>
@@ -40310,6 +40528,9 @@
       <c r="B29" t="s">
         <v>180</v>
       </c>
+      <c r="C29">
+        <v>30</v>
+      </c>
       <c r="H29">
         <v>1</v>
       </c>
@@ -40492,6 +40713,9 @@
       <c r="B30" t="s">
         <v>183</v>
       </c>
+      <c r="C30">
+        <v>30</v>
+      </c>
       <c r="H30">
         <v>1</v>
       </c>
@@ -40673,6 +40897,9 @@
       </c>
       <c r="B31" t="s">
         <v>184</v>
+      </c>
+      <c r="C31">
+        <v>30</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -41948,4035 +42175,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BM22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:65">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:65">
-      <c r="A2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H2">
-        <v>1.5</v>
-      </c>
-      <c r="I2">
-        <v>0.5</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <v>0.994</v>
-      </c>
-      <c r="Q2">
-        <v>0.988</v>
-      </c>
-      <c r="R2">
-        <v>0.982</v>
-      </c>
-      <c r="S2">
-        <v>0.976</v>
-      </c>
-      <c r="T2">
-        <v>0.97</v>
-      </c>
-      <c r="U2">
-        <v>0.964</v>
-      </c>
-      <c r="V2">
-        <v>0.958</v>
-      </c>
-      <c r="W2">
-        <v>0.952</v>
-      </c>
-      <c r="X2">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y2">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z2">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA2">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB2">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC2">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD2">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE2">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF2">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG2">
-        <v>0.892</v>
-      </c>
-      <c r="AH2">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI2">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ2">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK2">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL2">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM2">
-        <v>0.856</v>
-      </c>
-      <c r="AN2">
-        <v>0.85</v>
-      </c>
-      <c r="AO2">
-        <v>0.844</v>
-      </c>
-      <c r="AP2">
-        <v>0.838</v>
-      </c>
-      <c r="AQ2">
-        <v>0.832</v>
-      </c>
-      <c r="AR2">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS2">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT2">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU2">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV2">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW2">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX2">
-        <v>0.79</v>
-      </c>
-      <c r="AY2">
-        <v>0.784</v>
-      </c>
-      <c r="AZ2">
-        <v>0.778</v>
-      </c>
-      <c r="BA2">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB2">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC2">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD2">
-        <v>0.754</v>
-      </c>
-      <c r="BE2">
-        <v>0.748</v>
-      </c>
-      <c r="BF2">
-        <v>0.742</v>
-      </c>
-      <c r="BG2">
-        <v>0.736</v>
-      </c>
-      <c r="BH2">
-        <v>0.73</v>
-      </c>
-      <c r="BI2">
-        <v>0.724</v>
-      </c>
-      <c r="BJ2">
-        <v>0.718</v>
-      </c>
-      <c r="BK2">
-        <v>0.712</v>
-      </c>
-      <c r="BL2">
-        <v>0.706</v>
-      </c>
-      <c r="BM2">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:65">
-      <c r="A3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H3">
-        <v>1.5</v>
-      </c>
-      <c r="I3">
-        <v>0.5</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
-        <v>0.994</v>
-      </c>
-      <c r="Q3">
-        <v>0.988</v>
-      </c>
-      <c r="R3">
-        <v>0.982</v>
-      </c>
-      <c r="S3">
-        <v>0.976</v>
-      </c>
-      <c r="T3">
-        <v>0.97</v>
-      </c>
-      <c r="U3">
-        <v>0.964</v>
-      </c>
-      <c r="V3">
-        <v>0.958</v>
-      </c>
-      <c r="W3">
-        <v>0.952</v>
-      </c>
-      <c r="X3">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y3">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z3">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA3">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB3">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC3">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD3">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE3">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF3">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG3">
-        <v>0.892</v>
-      </c>
-      <c r="AH3">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI3">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ3">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK3">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL3">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM3">
-        <v>0.856</v>
-      </c>
-      <c r="AN3">
-        <v>0.85</v>
-      </c>
-      <c r="AO3">
-        <v>0.844</v>
-      </c>
-      <c r="AP3">
-        <v>0.838</v>
-      </c>
-      <c r="AQ3">
-        <v>0.832</v>
-      </c>
-      <c r="AR3">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS3">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT3">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU3">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV3">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW3">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX3">
-        <v>0.79</v>
-      </c>
-      <c r="AY3">
-        <v>0.784</v>
-      </c>
-      <c r="AZ3">
-        <v>0.778</v>
-      </c>
-      <c r="BA3">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB3">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC3">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD3">
-        <v>0.754</v>
-      </c>
-      <c r="BE3">
-        <v>0.748</v>
-      </c>
-      <c r="BF3">
-        <v>0.742</v>
-      </c>
-      <c r="BG3">
-        <v>0.736</v>
-      </c>
-      <c r="BH3">
-        <v>0.73</v>
-      </c>
-      <c r="BI3">
-        <v>0.724</v>
-      </c>
-      <c r="BJ3">
-        <v>0.718</v>
-      </c>
-      <c r="BK3">
-        <v>0.712</v>
-      </c>
-      <c r="BL3">
-        <v>0.706</v>
-      </c>
-      <c r="BM3">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:65">
-      <c r="A4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H4">
-        <v>1.5</v>
-      </c>
-      <c r="I4">
-        <v>0.5</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>0.994</v>
-      </c>
-      <c r="Q4">
-        <v>0.988</v>
-      </c>
-      <c r="R4">
-        <v>0.982</v>
-      </c>
-      <c r="S4">
-        <v>0.976</v>
-      </c>
-      <c r="T4">
-        <v>0.97</v>
-      </c>
-      <c r="U4">
-        <v>0.964</v>
-      </c>
-      <c r="V4">
-        <v>0.958</v>
-      </c>
-      <c r="W4">
-        <v>0.952</v>
-      </c>
-      <c r="X4">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y4">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z4">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA4">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB4">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC4">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD4">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE4">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF4">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG4">
-        <v>0.892</v>
-      </c>
-      <c r="AH4">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI4">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ4">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK4">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL4">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM4">
-        <v>0.856</v>
-      </c>
-      <c r="AN4">
-        <v>0.85</v>
-      </c>
-      <c r="AO4">
-        <v>0.844</v>
-      </c>
-      <c r="AP4">
-        <v>0.838</v>
-      </c>
-      <c r="AQ4">
-        <v>0.832</v>
-      </c>
-      <c r="AR4">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS4">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT4">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU4">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV4">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW4">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX4">
-        <v>0.79</v>
-      </c>
-      <c r="AY4">
-        <v>0.784</v>
-      </c>
-      <c r="AZ4">
-        <v>0.778</v>
-      </c>
-      <c r="BA4">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB4">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC4">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD4">
-        <v>0.754</v>
-      </c>
-      <c r="BE4">
-        <v>0.748</v>
-      </c>
-      <c r="BF4">
-        <v>0.742</v>
-      </c>
-      <c r="BG4">
-        <v>0.736</v>
-      </c>
-      <c r="BH4">
-        <v>0.73</v>
-      </c>
-      <c r="BI4">
-        <v>0.724</v>
-      </c>
-      <c r="BJ4">
-        <v>0.718</v>
-      </c>
-      <c r="BK4">
-        <v>0.712</v>
-      </c>
-      <c r="BL4">
-        <v>0.706</v>
-      </c>
-      <c r="BM4">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:65">
-      <c r="A5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H5">
-        <v>1.5</v>
-      </c>
-      <c r="I5">
-        <v>0.5</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>0.994</v>
-      </c>
-      <c r="Q5">
-        <v>0.988</v>
-      </c>
-      <c r="R5">
-        <v>0.982</v>
-      </c>
-      <c r="S5">
-        <v>0.976</v>
-      </c>
-      <c r="T5">
-        <v>0.97</v>
-      </c>
-      <c r="U5">
-        <v>0.964</v>
-      </c>
-      <c r="V5">
-        <v>0.958</v>
-      </c>
-      <c r="W5">
-        <v>0.952</v>
-      </c>
-      <c r="X5">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y5">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z5">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA5">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB5">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC5">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD5">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE5">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF5">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG5">
-        <v>0.892</v>
-      </c>
-      <c r="AH5">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI5">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ5">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK5">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL5">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM5">
-        <v>0.856</v>
-      </c>
-      <c r="AN5">
-        <v>0.85</v>
-      </c>
-      <c r="AO5">
-        <v>0.844</v>
-      </c>
-      <c r="AP5">
-        <v>0.838</v>
-      </c>
-      <c r="AQ5">
-        <v>0.832</v>
-      </c>
-      <c r="AR5">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS5">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT5">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU5">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV5">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW5">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX5">
-        <v>0.79</v>
-      </c>
-      <c r="AY5">
-        <v>0.784</v>
-      </c>
-      <c r="AZ5">
-        <v>0.778</v>
-      </c>
-      <c r="BA5">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB5">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC5">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD5">
-        <v>0.754</v>
-      </c>
-      <c r="BE5">
-        <v>0.748</v>
-      </c>
-      <c r="BF5">
-        <v>0.742</v>
-      </c>
-      <c r="BG5">
-        <v>0.736</v>
-      </c>
-      <c r="BH5">
-        <v>0.73</v>
-      </c>
-      <c r="BI5">
-        <v>0.724</v>
-      </c>
-      <c r="BJ5">
-        <v>0.718</v>
-      </c>
-      <c r="BK5">
-        <v>0.712</v>
-      </c>
-      <c r="BL5">
-        <v>0.706</v>
-      </c>
-      <c r="BM5">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:65">
-      <c r="A6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H6">
-        <v>1.5</v>
-      </c>
-      <c r="I6">
-        <v>0.5</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
-        <v>0.994</v>
-      </c>
-      <c r="Q6">
-        <v>0.988</v>
-      </c>
-      <c r="R6">
-        <v>0.982</v>
-      </c>
-      <c r="S6">
-        <v>0.976</v>
-      </c>
-      <c r="T6">
-        <v>0.97</v>
-      </c>
-      <c r="U6">
-        <v>0.964</v>
-      </c>
-      <c r="V6">
-        <v>0.958</v>
-      </c>
-      <c r="W6">
-        <v>0.952</v>
-      </c>
-      <c r="X6">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y6">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z6">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA6">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB6">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC6">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD6">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE6">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF6">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG6">
-        <v>0.892</v>
-      </c>
-      <c r="AH6">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI6">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ6">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK6">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL6">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM6">
-        <v>0.856</v>
-      </c>
-      <c r="AN6">
-        <v>0.85</v>
-      </c>
-      <c r="AO6">
-        <v>0.844</v>
-      </c>
-      <c r="AP6">
-        <v>0.838</v>
-      </c>
-      <c r="AQ6">
-        <v>0.832</v>
-      </c>
-      <c r="AR6">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS6">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT6">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU6">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV6">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW6">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX6">
-        <v>0.79</v>
-      </c>
-      <c r="AY6">
-        <v>0.784</v>
-      </c>
-      <c r="AZ6">
-        <v>0.778</v>
-      </c>
-      <c r="BA6">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB6">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC6">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD6">
-        <v>0.754</v>
-      </c>
-      <c r="BE6">
-        <v>0.748</v>
-      </c>
-      <c r="BF6">
-        <v>0.742</v>
-      </c>
-      <c r="BG6">
-        <v>0.736</v>
-      </c>
-      <c r="BH6">
-        <v>0.73</v>
-      </c>
-      <c r="BI6">
-        <v>0.724</v>
-      </c>
-      <c r="BJ6">
-        <v>0.718</v>
-      </c>
-      <c r="BK6">
-        <v>0.712</v>
-      </c>
-      <c r="BL6">
-        <v>0.706</v>
-      </c>
-      <c r="BM6">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:65">
-      <c r="A7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7">
-        <v>1.5</v>
-      </c>
-      <c r="I7">
-        <v>0.5</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>0.994</v>
-      </c>
-      <c r="Q7">
-        <v>0.988</v>
-      </c>
-      <c r="R7">
-        <v>0.982</v>
-      </c>
-      <c r="S7">
-        <v>0.976</v>
-      </c>
-      <c r="T7">
-        <v>0.97</v>
-      </c>
-      <c r="U7">
-        <v>0.964</v>
-      </c>
-      <c r="V7">
-        <v>0.958</v>
-      </c>
-      <c r="W7">
-        <v>0.952</v>
-      </c>
-      <c r="X7">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y7">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z7">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA7">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB7">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC7">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD7">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE7">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF7">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG7">
-        <v>0.892</v>
-      </c>
-      <c r="AH7">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI7">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ7">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK7">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL7">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM7">
-        <v>0.856</v>
-      </c>
-      <c r="AN7">
-        <v>0.85</v>
-      </c>
-      <c r="AO7">
-        <v>0.844</v>
-      </c>
-      <c r="AP7">
-        <v>0.838</v>
-      </c>
-      <c r="AQ7">
-        <v>0.832</v>
-      </c>
-      <c r="AR7">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS7">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT7">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU7">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV7">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW7">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX7">
-        <v>0.79</v>
-      </c>
-      <c r="AY7">
-        <v>0.784</v>
-      </c>
-      <c r="AZ7">
-        <v>0.778</v>
-      </c>
-      <c r="BA7">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB7">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC7">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD7">
-        <v>0.754</v>
-      </c>
-      <c r="BE7">
-        <v>0.748</v>
-      </c>
-      <c r="BF7">
-        <v>0.742</v>
-      </c>
-      <c r="BG7">
-        <v>0.736</v>
-      </c>
-      <c r="BH7">
-        <v>0.73</v>
-      </c>
-      <c r="BI7">
-        <v>0.724</v>
-      </c>
-      <c r="BJ7">
-        <v>0.718</v>
-      </c>
-      <c r="BK7">
-        <v>0.712</v>
-      </c>
-      <c r="BL7">
-        <v>0.706</v>
-      </c>
-      <c r="BM7">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:65">
-      <c r="A8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H8">
-        <v>1.5</v>
-      </c>
-      <c r="I8">
-        <v>0.5</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
-        <v>0.994</v>
-      </c>
-      <c r="Q8">
-        <v>0.988</v>
-      </c>
-      <c r="R8">
-        <v>0.982</v>
-      </c>
-      <c r="S8">
-        <v>0.976</v>
-      </c>
-      <c r="T8">
-        <v>0.97</v>
-      </c>
-      <c r="U8">
-        <v>0.964</v>
-      </c>
-      <c r="V8">
-        <v>0.958</v>
-      </c>
-      <c r="W8">
-        <v>0.952</v>
-      </c>
-      <c r="X8">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y8">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z8">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA8">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB8">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC8">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD8">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE8">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF8">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG8">
-        <v>0.892</v>
-      </c>
-      <c r="AH8">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI8">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ8">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK8">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL8">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM8">
-        <v>0.856</v>
-      </c>
-      <c r="AN8">
-        <v>0.85</v>
-      </c>
-      <c r="AO8">
-        <v>0.844</v>
-      </c>
-      <c r="AP8">
-        <v>0.838</v>
-      </c>
-      <c r="AQ8">
-        <v>0.832</v>
-      </c>
-      <c r="AR8">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS8">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT8">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU8">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV8">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW8">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX8">
-        <v>0.79</v>
-      </c>
-      <c r="AY8">
-        <v>0.784</v>
-      </c>
-      <c r="AZ8">
-        <v>0.778</v>
-      </c>
-      <c r="BA8">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB8">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC8">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD8">
-        <v>0.754</v>
-      </c>
-      <c r="BE8">
-        <v>0.748</v>
-      </c>
-      <c r="BF8">
-        <v>0.742</v>
-      </c>
-      <c r="BG8">
-        <v>0.736</v>
-      </c>
-      <c r="BH8">
-        <v>0.73</v>
-      </c>
-      <c r="BI8">
-        <v>0.724</v>
-      </c>
-      <c r="BJ8">
-        <v>0.718</v>
-      </c>
-      <c r="BK8">
-        <v>0.712</v>
-      </c>
-      <c r="BL8">
-        <v>0.706</v>
-      </c>
-      <c r="BM8">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:65">
-      <c r="A9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H9">
-        <v>1.5</v>
-      </c>
-      <c r="I9">
-        <v>0.5</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9">
-        <v>0.994</v>
-      </c>
-      <c r="Q9">
-        <v>0.988</v>
-      </c>
-      <c r="R9">
-        <v>0.982</v>
-      </c>
-      <c r="S9">
-        <v>0.976</v>
-      </c>
-      <c r="T9">
-        <v>0.97</v>
-      </c>
-      <c r="U9">
-        <v>0.964</v>
-      </c>
-      <c r="V9">
-        <v>0.958</v>
-      </c>
-      <c r="W9">
-        <v>0.952</v>
-      </c>
-      <c r="X9">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y9">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z9">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA9">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB9">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC9">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD9">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE9">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF9">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG9">
-        <v>0.892</v>
-      </c>
-      <c r="AH9">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI9">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ9">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK9">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL9">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM9">
-        <v>0.856</v>
-      </c>
-      <c r="AN9">
-        <v>0.85</v>
-      </c>
-      <c r="AO9">
-        <v>0.844</v>
-      </c>
-      <c r="AP9">
-        <v>0.838</v>
-      </c>
-      <c r="AQ9">
-        <v>0.832</v>
-      </c>
-      <c r="AR9">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS9">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT9">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU9">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV9">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW9">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX9">
-        <v>0.79</v>
-      </c>
-      <c r="AY9">
-        <v>0.784</v>
-      </c>
-      <c r="AZ9">
-        <v>0.778</v>
-      </c>
-      <c r="BA9">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB9">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC9">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD9">
-        <v>0.754</v>
-      </c>
-      <c r="BE9">
-        <v>0.748</v>
-      </c>
-      <c r="BF9">
-        <v>0.742</v>
-      </c>
-      <c r="BG9">
-        <v>0.736</v>
-      </c>
-      <c r="BH9">
-        <v>0.73</v>
-      </c>
-      <c r="BI9">
-        <v>0.724</v>
-      </c>
-      <c r="BJ9">
-        <v>0.718</v>
-      </c>
-      <c r="BK9">
-        <v>0.712</v>
-      </c>
-      <c r="BL9">
-        <v>0.706</v>
-      </c>
-      <c r="BM9">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:65">
-      <c r="A10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H10">
-        <v>1.5</v>
-      </c>
-      <c r="I10">
-        <v>0.5</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
-      <c r="P10">
-        <v>0.994</v>
-      </c>
-      <c r="Q10">
-        <v>0.988</v>
-      </c>
-      <c r="R10">
-        <v>0.982</v>
-      </c>
-      <c r="S10">
-        <v>0.976</v>
-      </c>
-      <c r="T10">
-        <v>0.97</v>
-      </c>
-      <c r="U10">
-        <v>0.964</v>
-      </c>
-      <c r="V10">
-        <v>0.958</v>
-      </c>
-      <c r="W10">
-        <v>0.952</v>
-      </c>
-      <c r="X10">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y10">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z10">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA10">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB10">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC10">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD10">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE10">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF10">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG10">
-        <v>0.892</v>
-      </c>
-      <c r="AH10">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI10">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ10">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK10">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL10">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM10">
-        <v>0.856</v>
-      </c>
-      <c r="AN10">
-        <v>0.85</v>
-      </c>
-      <c r="AO10">
-        <v>0.844</v>
-      </c>
-      <c r="AP10">
-        <v>0.838</v>
-      </c>
-      <c r="AQ10">
-        <v>0.832</v>
-      </c>
-      <c r="AR10">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS10">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT10">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU10">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV10">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW10">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX10">
-        <v>0.79</v>
-      </c>
-      <c r="AY10">
-        <v>0.784</v>
-      </c>
-      <c r="AZ10">
-        <v>0.778</v>
-      </c>
-      <c r="BA10">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB10">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC10">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD10">
-        <v>0.754</v>
-      </c>
-      <c r="BE10">
-        <v>0.748</v>
-      </c>
-      <c r="BF10">
-        <v>0.742</v>
-      </c>
-      <c r="BG10">
-        <v>0.736</v>
-      </c>
-      <c r="BH10">
-        <v>0.73</v>
-      </c>
-      <c r="BI10">
-        <v>0.724</v>
-      </c>
-      <c r="BJ10">
-        <v>0.718</v>
-      </c>
-      <c r="BK10">
-        <v>0.712</v>
-      </c>
-      <c r="BL10">
-        <v>0.706</v>
-      </c>
-      <c r="BM10">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:65">
-      <c r="A11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11">
-        <v>1.5</v>
-      </c>
-      <c r="I11">
-        <v>0.5</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="P11">
-        <v>0.994</v>
-      </c>
-      <c r="Q11">
-        <v>0.988</v>
-      </c>
-      <c r="R11">
-        <v>0.982</v>
-      </c>
-      <c r="S11">
-        <v>0.976</v>
-      </c>
-      <c r="T11">
-        <v>0.97</v>
-      </c>
-      <c r="U11">
-        <v>0.964</v>
-      </c>
-      <c r="V11">
-        <v>0.958</v>
-      </c>
-      <c r="W11">
-        <v>0.952</v>
-      </c>
-      <c r="X11">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y11">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z11">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA11">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB11">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC11">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD11">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE11">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF11">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG11">
-        <v>0.892</v>
-      </c>
-      <c r="AH11">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI11">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ11">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK11">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL11">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM11">
-        <v>0.856</v>
-      </c>
-      <c r="AN11">
-        <v>0.85</v>
-      </c>
-      <c r="AO11">
-        <v>0.844</v>
-      </c>
-      <c r="AP11">
-        <v>0.838</v>
-      </c>
-      <c r="AQ11">
-        <v>0.832</v>
-      </c>
-      <c r="AR11">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS11">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT11">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU11">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV11">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW11">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX11">
-        <v>0.79</v>
-      </c>
-      <c r="AY11">
-        <v>0.784</v>
-      </c>
-      <c r="AZ11">
-        <v>0.778</v>
-      </c>
-      <c r="BA11">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB11">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC11">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD11">
-        <v>0.754</v>
-      </c>
-      <c r="BE11">
-        <v>0.748</v>
-      </c>
-      <c r="BF11">
-        <v>0.742</v>
-      </c>
-      <c r="BG11">
-        <v>0.736</v>
-      </c>
-      <c r="BH11">
-        <v>0.73</v>
-      </c>
-      <c r="BI11">
-        <v>0.724</v>
-      </c>
-      <c r="BJ11">
-        <v>0.718</v>
-      </c>
-      <c r="BK11">
-        <v>0.712</v>
-      </c>
-      <c r="BL11">
-        <v>0.706</v>
-      </c>
-      <c r="BM11">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:65">
-      <c r="A12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="H12">
-        <v>1.5</v>
-      </c>
-      <c r="I12">
-        <v>0.5</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-      <c r="P12">
-        <v>0.994</v>
-      </c>
-      <c r="Q12">
-        <v>0.988</v>
-      </c>
-      <c r="R12">
-        <v>0.982</v>
-      </c>
-      <c r="S12">
-        <v>0.976</v>
-      </c>
-      <c r="T12">
-        <v>0.97</v>
-      </c>
-      <c r="U12">
-        <v>0.964</v>
-      </c>
-      <c r="V12">
-        <v>0.958</v>
-      </c>
-      <c r="W12">
-        <v>0.952</v>
-      </c>
-      <c r="X12">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y12">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z12">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA12">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB12">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC12">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD12">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE12">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF12">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG12">
-        <v>0.892</v>
-      </c>
-      <c r="AH12">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI12">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ12">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK12">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL12">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM12">
-        <v>0.856</v>
-      </c>
-      <c r="AN12">
-        <v>0.85</v>
-      </c>
-      <c r="AO12">
-        <v>0.844</v>
-      </c>
-      <c r="AP12">
-        <v>0.838</v>
-      </c>
-      <c r="AQ12">
-        <v>0.832</v>
-      </c>
-      <c r="AR12">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS12">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT12">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU12">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV12">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW12">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX12">
-        <v>0.79</v>
-      </c>
-      <c r="AY12">
-        <v>0.784</v>
-      </c>
-      <c r="AZ12">
-        <v>0.778</v>
-      </c>
-      <c r="BA12">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB12">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC12">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD12">
-        <v>0.754</v>
-      </c>
-      <c r="BE12">
-        <v>0.748</v>
-      </c>
-      <c r="BF12">
-        <v>0.742</v>
-      </c>
-      <c r="BG12">
-        <v>0.736</v>
-      </c>
-      <c r="BH12">
-        <v>0.73</v>
-      </c>
-      <c r="BI12">
-        <v>0.724</v>
-      </c>
-      <c r="BJ12">
-        <v>0.718</v>
-      </c>
-      <c r="BK12">
-        <v>0.712</v>
-      </c>
-      <c r="BL12">
-        <v>0.706</v>
-      </c>
-      <c r="BM12">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:65">
-      <c r="A13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" t="s">
-        <v>79</v>
-      </c>
-      <c r="H13">
-        <v>1.5</v>
-      </c>
-      <c r="I13">
-        <v>0.5</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13">
-        <v>1</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
-      <c r="P13">
-        <v>0.994</v>
-      </c>
-      <c r="Q13">
-        <v>0.988</v>
-      </c>
-      <c r="R13">
-        <v>0.982</v>
-      </c>
-      <c r="S13">
-        <v>0.976</v>
-      </c>
-      <c r="T13">
-        <v>0.97</v>
-      </c>
-      <c r="U13">
-        <v>0.964</v>
-      </c>
-      <c r="V13">
-        <v>0.958</v>
-      </c>
-      <c r="W13">
-        <v>0.952</v>
-      </c>
-      <c r="X13">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y13">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z13">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA13">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB13">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC13">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD13">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE13">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF13">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG13">
-        <v>0.892</v>
-      </c>
-      <c r="AH13">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI13">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ13">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK13">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL13">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM13">
-        <v>0.856</v>
-      </c>
-      <c r="AN13">
-        <v>0.85</v>
-      </c>
-      <c r="AO13">
-        <v>0.844</v>
-      </c>
-      <c r="AP13">
-        <v>0.838</v>
-      </c>
-      <c r="AQ13">
-        <v>0.832</v>
-      </c>
-      <c r="AR13">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS13">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT13">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU13">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV13">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW13">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX13">
-        <v>0.79</v>
-      </c>
-      <c r="AY13">
-        <v>0.784</v>
-      </c>
-      <c r="AZ13">
-        <v>0.778</v>
-      </c>
-      <c r="BA13">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB13">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC13">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD13">
-        <v>0.754</v>
-      </c>
-      <c r="BE13">
-        <v>0.748</v>
-      </c>
-      <c r="BF13">
-        <v>0.742</v>
-      </c>
-      <c r="BG13">
-        <v>0.736</v>
-      </c>
-      <c r="BH13">
-        <v>0.73</v>
-      </c>
-      <c r="BI13">
-        <v>0.724</v>
-      </c>
-      <c r="BJ13">
-        <v>0.718</v>
-      </c>
-      <c r="BK13">
-        <v>0.712</v>
-      </c>
-      <c r="BL13">
-        <v>0.706</v>
-      </c>
-      <c r="BM13">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:65">
-      <c r="A14" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" t="s">
-        <v>80</v>
-      </c>
-      <c r="H14">
-        <v>1.5</v>
-      </c>
-      <c r="I14">
-        <v>0.5</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
-        <v>1</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-      <c r="O14">
-        <v>1</v>
-      </c>
-      <c r="P14">
-        <v>0.994</v>
-      </c>
-      <c r="Q14">
-        <v>0.988</v>
-      </c>
-      <c r="R14">
-        <v>0.982</v>
-      </c>
-      <c r="S14">
-        <v>0.976</v>
-      </c>
-      <c r="T14">
-        <v>0.97</v>
-      </c>
-      <c r="U14">
-        <v>0.964</v>
-      </c>
-      <c r="V14">
-        <v>0.958</v>
-      </c>
-      <c r="W14">
-        <v>0.952</v>
-      </c>
-      <c r="X14">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y14">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z14">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA14">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB14">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC14">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD14">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE14">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF14">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG14">
-        <v>0.892</v>
-      </c>
-      <c r="AH14">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI14">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ14">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK14">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL14">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM14">
-        <v>0.856</v>
-      </c>
-      <c r="AN14">
-        <v>0.85</v>
-      </c>
-      <c r="AO14">
-        <v>0.844</v>
-      </c>
-      <c r="AP14">
-        <v>0.838</v>
-      </c>
-      <c r="AQ14">
-        <v>0.832</v>
-      </c>
-      <c r="AR14">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS14">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT14">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU14">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV14">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW14">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX14">
-        <v>0.79</v>
-      </c>
-      <c r="AY14">
-        <v>0.784</v>
-      </c>
-      <c r="AZ14">
-        <v>0.778</v>
-      </c>
-      <c r="BA14">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB14">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC14">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD14">
-        <v>0.754</v>
-      </c>
-      <c r="BE14">
-        <v>0.748</v>
-      </c>
-      <c r="BF14">
-        <v>0.742</v>
-      </c>
-      <c r="BG14">
-        <v>0.736</v>
-      </c>
-      <c r="BH14">
-        <v>0.73</v>
-      </c>
-      <c r="BI14">
-        <v>0.724</v>
-      </c>
-      <c r="BJ14">
-        <v>0.718</v>
-      </c>
-      <c r="BK14">
-        <v>0.712</v>
-      </c>
-      <c r="BL14">
-        <v>0.706</v>
-      </c>
-      <c r="BM14">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:65">
-      <c r="A15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" t="s">
-        <v>81</v>
-      </c>
-      <c r="H15">
-        <v>1.5</v>
-      </c>
-      <c r="I15">
-        <v>0.5</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15">
-        <v>1</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
-      <c r="O15">
-        <v>1</v>
-      </c>
-      <c r="P15">
-        <v>0.994</v>
-      </c>
-      <c r="Q15">
-        <v>0.988</v>
-      </c>
-      <c r="R15">
-        <v>0.982</v>
-      </c>
-      <c r="S15">
-        <v>0.976</v>
-      </c>
-      <c r="T15">
-        <v>0.97</v>
-      </c>
-      <c r="U15">
-        <v>0.964</v>
-      </c>
-      <c r="V15">
-        <v>0.958</v>
-      </c>
-      <c r="W15">
-        <v>0.952</v>
-      </c>
-      <c r="X15">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y15">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z15">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA15">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB15">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC15">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD15">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE15">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF15">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG15">
-        <v>0.892</v>
-      </c>
-      <c r="AH15">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI15">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ15">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK15">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL15">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM15">
-        <v>0.856</v>
-      </c>
-      <c r="AN15">
-        <v>0.85</v>
-      </c>
-      <c r="AO15">
-        <v>0.844</v>
-      </c>
-      <c r="AP15">
-        <v>0.838</v>
-      </c>
-      <c r="AQ15">
-        <v>0.832</v>
-      </c>
-      <c r="AR15">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS15">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT15">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU15">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV15">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW15">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX15">
-        <v>0.79</v>
-      </c>
-      <c r="AY15">
-        <v>0.784</v>
-      </c>
-      <c r="AZ15">
-        <v>0.778</v>
-      </c>
-      <c r="BA15">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB15">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC15">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD15">
-        <v>0.754</v>
-      </c>
-      <c r="BE15">
-        <v>0.748</v>
-      </c>
-      <c r="BF15">
-        <v>0.742</v>
-      </c>
-      <c r="BG15">
-        <v>0.736</v>
-      </c>
-      <c r="BH15">
-        <v>0.73</v>
-      </c>
-      <c r="BI15">
-        <v>0.724</v>
-      </c>
-      <c r="BJ15">
-        <v>0.718</v>
-      </c>
-      <c r="BK15">
-        <v>0.712</v>
-      </c>
-      <c r="BL15">
-        <v>0.706</v>
-      </c>
-      <c r="BM15">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:65">
-      <c r="A16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" t="s">
-        <v>82</v>
-      </c>
-      <c r="H16">
-        <v>1.5</v>
-      </c>
-      <c r="I16">
-        <v>0.5</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-      <c r="N16">
-        <v>1</v>
-      </c>
-      <c r="O16">
-        <v>1</v>
-      </c>
-      <c r="P16">
-        <v>0.994</v>
-      </c>
-      <c r="Q16">
-        <v>0.988</v>
-      </c>
-      <c r="R16">
-        <v>0.982</v>
-      </c>
-      <c r="S16">
-        <v>0.976</v>
-      </c>
-      <c r="T16">
-        <v>0.97</v>
-      </c>
-      <c r="U16">
-        <v>0.964</v>
-      </c>
-      <c r="V16">
-        <v>0.958</v>
-      </c>
-      <c r="W16">
-        <v>0.952</v>
-      </c>
-      <c r="X16">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y16">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z16">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA16">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB16">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC16">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD16">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE16">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF16">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG16">
-        <v>0.892</v>
-      </c>
-      <c r="AH16">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI16">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ16">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK16">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL16">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM16">
-        <v>0.856</v>
-      </c>
-      <c r="AN16">
-        <v>0.85</v>
-      </c>
-      <c r="AO16">
-        <v>0.844</v>
-      </c>
-      <c r="AP16">
-        <v>0.838</v>
-      </c>
-      <c r="AQ16">
-        <v>0.832</v>
-      </c>
-      <c r="AR16">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS16">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT16">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU16">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV16">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW16">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX16">
-        <v>0.79</v>
-      </c>
-      <c r="AY16">
-        <v>0.784</v>
-      </c>
-      <c r="AZ16">
-        <v>0.778</v>
-      </c>
-      <c r="BA16">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB16">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC16">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD16">
-        <v>0.754</v>
-      </c>
-      <c r="BE16">
-        <v>0.748</v>
-      </c>
-      <c r="BF16">
-        <v>0.742</v>
-      </c>
-      <c r="BG16">
-        <v>0.736</v>
-      </c>
-      <c r="BH16">
-        <v>0.73</v>
-      </c>
-      <c r="BI16">
-        <v>0.724</v>
-      </c>
-      <c r="BJ16">
-        <v>0.718</v>
-      </c>
-      <c r="BK16">
-        <v>0.712</v>
-      </c>
-      <c r="BL16">
-        <v>0.706</v>
-      </c>
-      <c r="BM16">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:65">
-      <c r="A17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" t="s">
-        <v>83</v>
-      </c>
-      <c r="H17">
-        <v>1.5</v>
-      </c>
-      <c r="I17">
-        <v>0.5</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17">
-        <v>1</v>
-      </c>
-      <c r="O17">
-        <v>1</v>
-      </c>
-      <c r="P17">
-        <v>0.994</v>
-      </c>
-      <c r="Q17">
-        <v>0.988</v>
-      </c>
-      <c r="R17">
-        <v>0.982</v>
-      </c>
-      <c r="S17">
-        <v>0.976</v>
-      </c>
-      <c r="T17">
-        <v>0.97</v>
-      </c>
-      <c r="U17">
-        <v>0.964</v>
-      </c>
-      <c r="V17">
-        <v>0.958</v>
-      </c>
-      <c r="W17">
-        <v>0.952</v>
-      </c>
-      <c r="X17">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y17">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z17">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA17">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB17">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC17">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD17">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE17">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF17">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG17">
-        <v>0.892</v>
-      </c>
-      <c r="AH17">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI17">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ17">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK17">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL17">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM17">
-        <v>0.856</v>
-      </c>
-      <c r="AN17">
-        <v>0.85</v>
-      </c>
-      <c r="AO17">
-        <v>0.844</v>
-      </c>
-      <c r="AP17">
-        <v>0.838</v>
-      </c>
-      <c r="AQ17">
-        <v>0.832</v>
-      </c>
-      <c r="AR17">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS17">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT17">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU17">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV17">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW17">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX17">
-        <v>0.79</v>
-      </c>
-      <c r="AY17">
-        <v>0.784</v>
-      </c>
-      <c r="AZ17">
-        <v>0.778</v>
-      </c>
-      <c r="BA17">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB17">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC17">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD17">
-        <v>0.754</v>
-      </c>
-      <c r="BE17">
-        <v>0.748</v>
-      </c>
-      <c r="BF17">
-        <v>0.742</v>
-      </c>
-      <c r="BG17">
-        <v>0.736</v>
-      </c>
-      <c r="BH17">
-        <v>0.73</v>
-      </c>
-      <c r="BI17">
-        <v>0.724</v>
-      </c>
-      <c r="BJ17">
-        <v>0.718</v>
-      </c>
-      <c r="BK17">
-        <v>0.712</v>
-      </c>
-      <c r="BL17">
-        <v>0.706</v>
-      </c>
-      <c r="BM17">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:65">
-      <c r="A18" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18">
-        <v>1.5</v>
-      </c>
-      <c r="I18">
-        <v>0.5</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="N18">
-        <v>1</v>
-      </c>
-      <c r="O18">
-        <v>1</v>
-      </c>
-      <c r="P18">
-        <v>0.994</v>
-      </c>
-      <c r="Q18">
-        <v>0.988</v>
-      </c>
-      <c r="R18">
-        <v>0.982</v>
-      </c>
-      <c r="S18">
-        <v>0.976</v>
-      </c>
-      <c r="T18">
-        <v>0.97</v>
-      </c>
-      <c r="U18">
-        <v>0.964</v>
-      </c>
-      <c r="V18">
-        <v>0.958</v>
-      </c>
-      <c r="W18">
-        <v>0.952</v>
-      </c>
-      <c r="X18">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y18">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z18">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA18">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB18">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC18">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD18">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE18">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF18">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG18">
-        <v>0.892</v>
-      </c>
-      <c r="AH18">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI18">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ18">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK18">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL18">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM18">
-        <v>0.856</v>
-      </c>
-      <c r="AN18">
-        <v>0.85</v>
-      </c>
-      <c r="AO18">
-        <v>0.844</v>
-      </c>
-      <c r="AP18">
-        <v>0.838</v>
-      </c>
-      <c r="AQ18">
-        <v>0.832</v>
-      </c>
-      <c r="AR18">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS18">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT18">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU18">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV18">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW18">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX18">
-        <v>0.79</v>
-      </c>
-      <c r="AY18">
-        <v>0.784</v>
-      </c>
-      <c r="AZ18">
-        <v>0.778</v>
-      </c>
-      <c r="BA18">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB18">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC18">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD18">
-        <v>0.754</v>
-      </c>
-      <c r="BE18">
-        <v>0.748</v>
-      </c>
-      <c r="BF18">
-        <v>0.742</v>
-      </c>
-      <c r="BG18">
-        <v>0.736</v>
-      </c>
-      <c r="BH18">
-        <v>0.73</v>
-      </c>
-      <c r="BI18">
-        <v>0.724</v>
-      </c>
-      <c r="BJ18">
-        <v>0.718</v>
-      </c>
-      <c r="BK18">
-        <v>0.712</v>
-      </c>
-      <c r="BL18">
-        <v>0.706</v>
-      </c>
-      <c r="BM18">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:65">
-      <c r="A19" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" t="s">
-        <v>85</v>
-      </c>
-      <c r="H19">
-        <v>1.5</v>
-      </c>
-      <c r="I19">
-        <v>0.5</v>
-      </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-      <c r="O19">
-        <v>1</v>
-      </c>
-      <c r="P19">
-        <v>0.994</v>
-      </c>
-      <c r="Q19">
-        <v>0.988</v>
-      </c>
-      <c r="R19">
-        <v>0.982</v>
-      </c>
-      <c r="S19">
-        <v>0.976</v>
-      </c>
-      <c r="T19">
-        <v>0.97</v>
-      </c>
-      <c r="U19">
-        <v>0.964</v>
-      </c>
-      <c r="V19">
-        <v>0.958</v>
-      </c>
-      <c r="W19">
-        <v>0.952</v>
-      </c>
-      <c r="X19">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y19">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z19">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA19">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB19">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC19">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD19">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE19">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF19">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG19">
-        <v>0.892</v>
-      </c>
-      <c r="AH19">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI19">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ19">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK19">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL19">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM19">
-        <v>0.856</v>
-      </c>
-      <c r="AN19">
-        <v>0.85</v>
-      </c>
-      <c r="AO19">
-        <v>0.844</v>
-      </c>
-      <c r="AP19">
-        <v>0.838</v>
-      </c>
-      <c r="AQ19">
-        <v>0.832</v>
-      </c>
-      <c r="AR19">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS19">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT19">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU19">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV19">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW19">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX19">
-        <v>0.79</v>
-      </c>
-      <c r="AY19">
-        <v>0.784</v>
-      </c>
-      <c r="AZ19">
-        <v>0.778</v>
-      </c>
-      <c r="BA19">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB19">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC19">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD19">
-        <v>0.754</v>
-      </c>
-      <c r="BE19">
-        <v>0.748</v>
-      </c>
-      <c r="BF19">
-        <v>0.742</v>
-      </c>
-      <c r="BG19">
-        <v>0.736</v>
-      </c>
-      <c r="BH19">
-        <v>0.73</v>
-      </c>
-      <c r="BI19">
-        <v>0.724</v>
-      </c>
-      <c r="BJ19">
-        <v>0.718</v>
-      </c>
-      <c r="BK19">
-        <v>0.712</v>
-      </c>
-      <c r="BL19">
-        <v>0.706</v>
-      </c>
-      <c r="BM19">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:65">
-      <c r="A20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" t="s">
-        <v>86</v>
-      </c>
-      <c r="H20">
-        <v>1.5</v>
-      </c>
-      <c r="I20">
-        <v>0.5</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
-      <c r="O20">
-        <v>1</v>
-      </c>
-      <c r="P20">
-        <v>0.994</v>
-      </c>
-      <c r="Q20">
-        <v>0.988</v>
-      </c>
-      <c r="R20">
-        <v>0.982</v>
-      </c>
-      <c r="S20">
-        <v>0.976</v>
-      </c>
-      <c r="T20">
-        <v>0.97</v>
-      </c>
-      <c r="U20">
-        <v>0.964</v>
-      </c>
-      <c r="V20">
-        <v>0.958</v>
-      </c>
-      <c r="W20">
-        <v>0.952</v>
-      </c>
-      <c r="X20">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y20">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z20">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA20">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB20">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC20">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD20">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE20">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF20">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG20">
-        <v>0.892</v>
-      </c>
-      <c r="AH20">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI20">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ20">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK20">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL20">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM20">
-        <v>0.856</v>
-      </c>
-      <c r="AN20">
-        <v>0.85</v>
-      </c>
-      <c r="AO20">
-        <v>0.844</v>
-      </c>
-      <c r="AP20">
-        <v>0.838</v>
-      </c>
-      <c r="AQ20">
-        <v>0.832</v>
-      </c>
-      <c r="AR20">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS20">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT20">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU20">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV20">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW20">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX20">
-        <v>0.79</v>
-      </c>
-      <c r="AY20">
-        <v>0.784</v>
-      </c>
-      <c r="AZ20">
-        <v>0.778</v>
-      </c>
-      <c r="BA20">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB20">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC20">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD20">
-        <v>0.754</v>
-      </c>
-      <c r="BE20">
-        <v>0.748</v>
-      </c>
-      <c r="BF20">
-        <v>0.742</v>
-      </c>
-      <c r="BG20">
-        <v>0.736</v>
-      </c>
-      <c r="BH20">
-        <v>0.73</v>
-      </c>
-      <c r="BI20">
-        <v>0.724</v>
-      </c>
-      <c r="BJ20">
-        <v>0.718</v>
-      </c>
-      <c r="BK20">
-        <v>0.712</v>
-      </c>
-      <c r="BL20">
-        <v>0.706</v>
-      </c>
-      <c r="BM20">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:65">
-      <c r="A21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" t="s">
-        <v>87</v>
-      </c>
-      <c r="H21">
-        <v>1.5</v>
-      </c>
-      <c r="I21">
-        <v>0.5</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
-      <c r="L21">
-        <v>1</v>
-      </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-      <c r="N21">
-        <v>1</v>
-      </c>
-      <c r="O21">
-        <v>1</v>
-      </c>
-      <c r="P21">
-        <v>0.994</v>
-      </c>
-      <c r="Q21">
-        <v>0.988</v>
-      </c>
-      <c r="R21">
-        <v>0.982</v>
-      </c>
-      <c r="S21">
-        <v>0.976</v>
-      </c>
-      <c r="T21">
-        <v>0.97</v>
-      </c>
-      <c r="U21">
-        <v>0.964</v>
-      </c>
-      <c r="V21">
-        <v>0.958</v>
-      </c>
-      <c r="W21">
-        <v>0.952</v>
-      </c>
-      <c r="X21">
-        <v>0.9460000000000001</v>
-      </c>
-      <c r="Y21">
-        <v>0.9400000000000001</v>
-      </c>
-      <c r="Z21">
-        <v>0.9340000000000001</v>
-      </c>
-      <c r="AA21">
-        <v>0.9279999999999999</v>
-      </c>
-      <c r="AB21">
-        <v>0.9219999999999999</v>
-      </c>
-      <c r="AC21">
-        <v>0.9159999999999999</v>
-      </c>
-      <c r="AD21">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="AE21">
-        <v>0.9039999999999999</v>
-      </c>
-      <c r="AF21">
-        <v>0.8979999999999999</v>
-      </c>
-      <c r="AG21">
-        <v>0.892</v>
-      </c>
-      <c r="AH21">
-        <v>0.8859999999999999</v>
-      </c>
-      <c r="AI21">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="AJ21">
-        <v>0.8740000000000001</v>
-      </c>
-      <c r="AK21">
-        <v>0.8680000000000001</v>
-      </c>
-      <c r="AL21">
-        <v>0.8620000000000001</v>
-      </c>
-      <c r="AM21">
-        <v>0.856</v>
-      </c>
-      <c r="AN21">
-        <v>0.85</v>
-      </c>
-      <c r="AO21">
-        <v>0.844</v>
-      </c>
-      <c r="AP21">
-        <v>0.838</v>
-      </c>
-      <c r="AQ21">
-        <v>0.832</v>
-      </c>
-      <c r="AR21">
-        <v>0.8260000000000001</v>
-      </c>
-      <c r="AS21">
-        <v>0.8200000000000001</v>
-      </c>
-      <c r="AT21">
-        <v>0.8140000000000001</v>
-      </c>
-      <c r="AU21">
-        <v>0.8079999999999999</v>
-      </c>
-      <c r="AV21">
-        <v>0.8019999999999999</v>
-      </c>
-      <c r="AW21">
-        <v>0.7959999999999999</v>
-      </c>
-      <c r="AX21">
-        <v>0.79</v>
-      </c>
-      <c r="AY21">
-        <v>0.784</v>
-      </c>
-      <c r="AZ21">
-        <v>0.778</v>
-      </c>
-      <c r="BA21">
-        <v>0.7719999999999999</v>
-      </c>
-      <c r="BB21">
-        <v>0.7659999999999999</v>
-      </c>
-      <c r="BC21">
-        <v>0.7599999999999999</v>
-      </c>
-      <c r="BD21">
-        <v>0.754</v>
-      </c>
-      <c r="BE21">
-        <v>0.748</v>
-      </c>
-      <c r="BF21">
-        <v>0.742</v>
-      </c>
-      <c r="BG21">
-        <v>0.736</v>
-      </c>
-      <c r="BH21">
-        <v>0.73</v>
-      </c>
-      <c r="BI21">
-        <v>0.724</v>
-      </c>
-      <c r="BJ21">
-        <v>0.718</v>
-      </c>
-      <c r="BK21">
-        <v>0.712</v>
-      </c>
-      <c r="BL21">
-        <v>0.706</v>
-      </c>
-      <c r="BM21">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:65">
-      <c r="A22" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <v>0.72</v>
-      </c>
-      <c r="K22">
-        <v>0.72</v>
-      </c>
-      <c r="L22">
-        <v>0.72</v>
-      </c>
-      <c r="M22">
-        <v>0.72</v>
-      </c>
-      <c r="N22">
-        <v>0.72</v>
-      </c>
-      <c r="O22">
-        <v>0.72</v>
-      </c>
-      <c r="P22">
-        <v>0.7156</v>
-      </c>
-      <c r="Q22">
-        <v>0.7111999999999999</v>
-      </c>
-      <c r="R22">
-        <v>0.7068</v>
-      </c>
-      <c r="S22">
-        <v>0.7024</v>
-      </c>
-      <c r="T22">
-        <v>0.6980000000000001</v>
-      </c>
-      <c r="U22">
-        <v>0.6936</v>
-      </c>
-      <c r="V22">
-        <v>0.6892</v>
-      </c>
-      <c r="W22">
-        <v>0.6848</v>
-      </c>
-      <c r="X22">
-        <v>0.6804</v>
-      </c>
-      <c r="Y22">
-        <v>0.6759999999999999</v>
-      </c>
-      <c r="Z22">
-        <v>0.6716</v>
-      </c>
-      <c r="AA22">
-        <v>0.6672</v>
-      </c>
-      <c r="AB22">
-        <v>0.6627999999999999</v>
-      </c>
-      <c r="AC22">
-        <v>0.6584</v>
-      </c>
-      <c r="AD22">
-        <v>0.654</v>
-      </c>
-      <c r="AE22">
-        <v>0.6496</v>
-      </c>
-      <c r="AF22">
-        <v>0.6451999999999999</v>
-      </c>
-      <c r="AG22">
-        <v>0.6408</v>
-      </c>
-      <c r="AH22">
-        <v>0.6364</v>
-      </c>
-      <c r="AI22">
-        <v>0.632</v>
-      </c>
-      <c r="AJ22">
-        <v>0.6276</v>
-      </c>
-      <c r="AK22">
-        <v>0.6232</v>
-      </c>
-      <c r="AL22">
-        <v>0.6188</v>
-      </c>
-      <c r="AM22">
-        <v>0.6144000000000001</v>
-      </c>
-      <c r="AN22">
-        <v>0.61</v>
-      </c>
-      <c r="AO22">
-        <v>0.6055999999999999</v>
-      </c>
-      <c r="AP22">
-        <v>0.6012</v>
-      </c>
-      <c r="AQ22">
-        <v>0.5968</v>
-      </c>
-      <c r="AR22">
-        <v>0.5924</v>
-      </c>
-      <c r="AS22">
-        <v>0.588</v>
-      </c>
-      <c r="AT22">
-        <v>0.5836</v>
-      </c>
-      <c r="AU22">
-        <v>0.5791999999999999</v>
-      </c>
-      <c r="AV22">
-        <v>0.5748</v>
-      </c>
-      <c r="AW22">
-        <v>0.5704</v>
-      </c>
-      <c r="AX22">
-        <v>0.5660000000000001</v>
-      </c>
-      <c r="AY22">
-        <v>0.5616</v>
-      </c>
-      <c r="AZ22">
-        <v>0.5572</v>
-      </c>
-      <c r="BA22">
-        <v>0.5528</v>
-      </c>
-      <c r="BB22">
-        <v>0.5484</v>
-      </c>
-      <c r="BC22">
-        <v>0.544</v>
-      </c>
-      <c r="BD22">
-        <v>0.5396</v>
-      </c>
-      <c r="BE22">
-        <v>0.5352</v>
-      </c>
-      <c r="BF22">
-        <v>0.5307999999999999</v>
-      </c>
-      <c r="BG22">
-        <v>0.5264</v>
-      </c>
-      <c r="BH22">
-        <v>0.522</v>
-      </c>
-      <c r="BI22">
-        <v>0.5175999999999999</v>
-      </c>
-      <c r="BJ22">
-        <v>0.5132</v>
-      </c>
-      <c r="BK22">
-        <v>0.5088</v>
-      </c>
-      <c r="BL22">
-        <v>0.5044</v>
-      </c>
-      <c r="BM22">
-        <v>0.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:BM2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -46184,6 +42382,9 @@
       <c r="B2" t="s">
         <v>178</v>
       </c>
+      <c r="C2">
+        <v>15</v>
+      </c>
       <c r="H2">
         <v>1</v>
       </c>

--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ip_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ip_calibrated.xlsx
@@ -10,13 +10,14 @@
     <sheet name="strategy_id-0" sheetId="1" r:id="rId1"/>
     <sheet name="strategy_id-6004" sheetId="2" r:id="rId2"/>
     <sheet name="strategy_id-6008" sheetId="3" r:id="rId3"/>
+    <sheet name="strategy_id-6009" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="252">
   <si>
     <t>subsector</t>
   </si>
@@ -42563,4 +42564,396 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:BM2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:65">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:65">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2">
+        <v>15</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>0.72</v>
+      </c>
+      <c r="K2">
+        <v>0.72</v>
+      </c>
+      <c r="L2">
+        <v>0.72</v>
+      </c>
+      <c r="M2">
+        <v>0.72</v>
+      </c>
+      <c r="N2">
+        <v>0.72</v>
+      </c>
+      <c r="O2">
+        <v>0.72</v>
+      </c>
+      <c r="P2">
+        <v>0.72</v>
+      </c>
+      <c r="Q2">
+        <v>0.72</v>
+      </c>
+      <c r="R2">
+        <v>0.72</v>
+      </c>
+      <c r="S2">
+        <v>0.72</v>
+      </c>
+      <c r="T2">
+        <v>0.72</v>
+      </c>
+      <c r="U2">
+        <v>0.72</v>
+      </c>
+      <c r="V2">
+        <v>0.715</v>
+      </c>
+      <c r="W2">
+        <v>0.71</v>
+      </c>
+      <c r="X2">
+        <v>0.705</v>
+      </c>
+      <c r="Y2">
+        <v>0.7</v>
+      </c>
+      <c r="Z2">
+        <v>0.695</v>
+      </c>
+      <c r="AA2">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="AC2">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="AD2">
+        <v>0.6749999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0.6699999999999999</v>
+      </c>
+      <c r="AF2">
+        <v>0.665</v>
+      </c>
+      <c r="AG2">
+        <v>0.66</v>
+      </c>
+      <c r="AH2">
+        <v>0.655</v>
+      </c>
+      <c r="AI2">
+        <v>0.65</v>
+      </c>
+      <c r="AJ2">
+        <v>0.645</v>
+      </c>
+      <c r="AK2">
+        <v>0.6399999999999999</v>
+      </c>
+      <c r="AL2">
+        <v>0.635</v>
+      </c>
+      <c r="AM2">
+        <v>0.6299999999999999</v>
+      </c>
+      <c r="AN2">
+        <v>0.6249999999999999</v>
+      </c>
+      <c r="AO2">
+        <v>0.62</v>
+      </c>
+      <c r="AP2">
+        <v>0.615</v>
+      </c>
+      <c r="AQ2">
+        <v>0.61</v>
+      </c>
+      <c r="AR2">
+        <v>0.605</v>
+      </c>
+      <c r="AS2">
+        <v>0.6</v>
+      </c>
+      <c r="AT2">
+        <v>0.595</v>
+      </c>
+      <c r="AU2">
+        <v>0.59</v>
+      </c>
+      <c r="AV2">
+        <v>0.585</v>
+      </c>
+      <c r="AW2">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="AX2">
+        <v>0.575</v>
+      </c>
+      <c r="AY2">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="AZ2">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="BA2">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BB2">
+        <v>0.5549999999999999</v>
+      </c>
+      <c r="BC2">
+        <v>0.55</v>
+      </c>
+      <c r="BD2">
+        <v>0.545</v>
+      </c>
+      <c r="BE2">
+        <v>0.54</v>
+      </c>
+      <c r="BF2">
+        <v>0.535</v>
+      </c>
+      <c r="BG2">
+        <v>0.53</v>
+      </c>
+      <c r="BH2">
+        <v>0.525</v>
+      </c>
+      <c r="BI2">
+        <v>0.52</v>
+      </c>
+      <c r="BJ2">
+        <v>0.515</v>
+      </c>
+      <c r="BK2">
+        <v>0.51</v>
+      </c>
+      <c r="BL2">
+        <v>0.505</v>
+      </c>
+      <c r="BM2">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ip_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ip_calibrated.xlsx
@@ -18644,7 +18644,7 @@
         <v>161</v>
       </c>
       <c r="C97">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H97">
         <v>1.25</v>
@@ -18677,148 +18677,148 @@
         <v>1</v>
       </c>
       <c r="R97">
-        <v>1</v>
+        <v>1.003130681678704</v>
       </c>
       <c r="S97">
-        <v>1</v>
+        <v>1.045274038608246</v>
       </c>
       <c r="T97">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="U97">
-        <v>1</v>
+        <v>1.654725961391754</v>
       </c>
       <c r="V97">
-        <v>1</v>
+        <v>1.696869318321296</v>
       </c>
       <c r="W97">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="X97">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="Y97">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="Z97">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AA97">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AB97">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AC97">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AD97">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AE97">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AF97">
-        <v>1</v>
+        <v>1.671834690285538</v>
       </c>
       <c r="AG97">
-        <v>1</v>
+        <v>1.631835570475344</v>
       </c>
       <c r="AH97">
-        <v>1</v>
+        <v>1.576504621666405</v>
       </c>
       <c r="AI97">
-        <v>1</v>
+        <v>1.502685427118821</v>
       </c>
       <c r="AJ97">
-        <v>1</v>
+        <v>1.408815439581372</v>
       </c>
       <c r="AK97">
-        <v>1</v>
+        <v>1.296472053141829</v>
       </c>
       <c r="AL97">
-        <v>1</v>
+        <v>1.171379495906813</v>
       </c>
       <c r="AM97">
-        <v>1</v>
+        <v>1.042803123641231</v>
       </c>
       <c r="AN97">
-        <v>1</v>
+        <v>0.9210703799887764</v>
       </c>
       <c r="AO97">
-        <v>1</v>
+        <v>0.8144605141923096</v>
       </c>
       <c r="AP97">
-        <v>1</v>
+        <v>0.7272846426897402</v>
       </c>
       <c r="AQ97">
-        <v>1</v>
+        <v>0.6599118341558611</v>
       </c>
       <c r="AR97">
-        <v>1</v>
+        <v>0.610079623952921</v>
       </c>
       <c r="AS97">
-        <v>1</v>
+        <v>0.5744052933538932</v>
       </c>
       <c r="AT97">
-        <v>1</v>
+        <v>0.5494591461000103</v>
       </c>
       <c r="AU97">
-        <v>1</v>
+        <v>0.5323000342119495</v>
       </c>
       <c r="AV97">
-        <v>1</v>
+        <v>0.5206305664994517</v>
       </c>
       <c r="AW97">
-        <v>1</v>
+        <v>0.5127556678667879</v>
       </c>
       <c r="AX97">
-        <v>1</v>
+        <v>0.5074691822446702</v>
       </c>
       <c r="AY97">
-        <v>1</v>
+        <v>0.5039327713370252</v>
       </c>
       <c r="AZ97">
-        <v>1</v>
+        <v>0.5015726371694283</v>
       </c>
       <c r="BA97">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BB97">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BC97">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BD97">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BE97">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BF97">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BG97">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BH97">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BI97">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BJ97">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BK97">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BL97">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BM97">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="98" spans="1:65">
@@ -18829,7 +18829,7 @@
         <v>162</v>
       </c>
       <c r="C98">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H98">
         <v>1.25</v>
@@ -19014,7 +19014,7 @@
         <v>163</v>
       </c>
       <c r="C99">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H99">
         <v>1.25</v>
@@ -19199,7 +19199,7 @@
         <v>164</v>
       </c>
       <c r="C100">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H100">
         <v>1.25</v>
@@ -19384,7 +19384,7 @@
         <v>165</v>
       </c>
       <c r="C101">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H101">
         <v>1.25</v>
@@ -19569,7 +19569,7 @@
         <v>166</v>
       </c>
       <c r="C102">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H102">
         <v>1.25</v>
@@ -19599,151 +19599,151 @@
         <v>1.134855932203389</v>
       </c>
       <c r="Q102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="R102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="S102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="T102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="U102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="V102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="W102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="X102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="Y102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="Z102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AA102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AB102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AC102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AD102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AE102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AF102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AG102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AH102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AI102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AJ102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AK102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AL102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AM102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AN102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AO102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AP102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AQ102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AR102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AS102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AT102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AU102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AV102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AW102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AX102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AY102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AZ102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="BA102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="BB102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="BC102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="BD102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="BE102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="BF102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="BG102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="BH102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="BI102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="BJ102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="BL102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="BM102">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="103" spans="1:65">
@@ -19754,7 +19754,7 @@
         <v>167</v>
       </c>
       <c r="C103">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H103">
         <v>1.25</v>
@@ -19939,7 +19939,7 @@
         <v>168</v>
       </c>
       <c r="C104">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H104">
         <v>1.25</v>
@@ -20124,7 +20124,7 @@
         <v>169</v>
       </c>
       <c r="C105">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H105">
         <v>1.25</v>
@@ -20309,7 +20309,7 @@
         <v>170</v>
       </c>
       <c r="C106">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H106">
         <v>1.25</v>
@@ -20494,7 +20494,7 @@
         <v>171</v>
       </c>
       <c r="C107">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H107">
         <v>1.25</v>
@@ -20679,7 +20679,7 @@
         <v>172</v>
       </c>
       <c r="C108">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H108">
         <v>1.25</v>
@@ -20864,7 +20864,7 @@
         <v>173</v>
       </c>
       <c r="C109">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H109">
         <v>1.25</v>
@@ -21049,7 +21049,7 @@
         <v>174</v>
       </c>
       <c r="C110">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H110">
         <v>1.25</v>
@@ -21234,7 +21234,7 @@
         <v>175</v>
       </c>
       <c r="C111">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H111">
         <v>1.25</v>
@@ -21419,7 +21419,7 @@
         <v>176</v>
       </c>
       <c r="C112">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H112">
         <v>1.25</v>

--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ip_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_ip_calibrated.xlsx
@@ -53315,136 +53315,136 @@
         <v>0.72</v>
       </c>
       <c r="V7">
-        <v>0.72</v>
+        <v>0.715</v>
       </c>
       <c r="W7">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="X7">
-        <v>0.72</v>
+        <v>0.705</v>
       </c>
       <c r="Y7">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="Z7">
-        <v>0.72</v>
+        <v>0.695</v>
       </c>
       <c r="AA7">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AB7">
-        <v>0.72</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AC7">
-        <v>0.72</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="AD7">
-        <v>0.72</v>
+        <v>0.6749999999999999</v>
       </c>
       <c r="AE7">
-        <v>0.72</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="AF7">
-        <v>0.72</v>
+        <v>0.665</v>
       </c>
       <c r="AG7">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="AH7">
-        <v>0.7200000000000001</v>
+        <v>0.655</v>
       </c>
       <c r="AI7">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="AJ7">
-        <v>0.72</v>
+        <v>0.645</v>
       </c>
       <c r="AK7">
-        <v>0.72</v>
+        <v>0.6399999999999999</v>
       </c>
       <c r="AL7">
-        <v>0.72</v>
+        <v>0.635</v>
       </c>
       <c r="AM7">
-        <v>0.72</v>
+        <v>0.6299999999999999</v>
       </c>
       <c r="AN7">
-        <v>0.72</v>
+        <v>0.6249999999999999</v>
       </c>
       <c r="AO7">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="AP7">
-        <v>0.72</v>
+        <v>0.615</v>
       </c>
       <c r="AQ7">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="AR7">
-        <v>0.72</v>
+        <v>0.605</v>
       </c>
       <c r="AS7">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="AT7">
-        <v>0.72</v>
+        <v>0.595</v>
       </c>
       <c r="AU7">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="AV7">
-        <v>0.72</v>
+        <v>0.585</v>
       </c>
       <c r="AW7">
-        <v>0.72</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="AX7">
-        <v>0.72</v>
+        <v>0.575</v>
       </c>
       <c r="AY7">
-        <v>0.72</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="AZ7">
-        <v>0.72</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="BA7">
-        <v>0.72</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BB7">
-        <v>0.72</v>
+        <v>0.5549999999999999</v>
       </c>
       <c r="BC7">
-        <v>0.72</v>
+        <v>0.55</v>
       </c>
       <c r="BD7">
-        <v>0.72</v>
+        <v>0.545</v>
       </c>
       <c r="BE7">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="BF7">
-        <v>0.72</v>
+        <v>0.535</v>
       </c>
       <c r="BG7">
-        <v>0.72</v>
+        <v>0.53</v>
       </c>
       <c r="BH7">
-        <v>0.72</v>
+        <v>0.525</v>
       </c>
       <c r="BI7">
-        <v>0.72</v>
+        <v>0.52</v>
       </c>
       <c r="BJ7">
-        <v>0.72</v>
+        <v>0.515</v>
       </c>
       <c r="BK7">
-        <v>0.72</v>
+        <v>0.51</v>
       </c>
       <c r="BL7">
-        <v>0.72</v>
+        <v>0.505</v>
       </c>
       <c r="BM7">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8" spans="1:65">
@@ -56311,136 +56311,136 @@
         <v>0.72</v>
       </c>
       <c r="V2">
-        <v>0.72</v>
+        <v>0.715</v>
       </c>
       <c r="W2">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="X2">
-        <v>0.72</v>
+        <v>0.705</v>
       </c>
       <c r="Y2">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="Z2">
-        <v>0.72</v>
+        <v>0.695</v>
       </c>
       <c r="AA2">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AB2">
-        <v>0.72</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AC2">
-        <v>0.72</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="AD2">
-        <v>0.72</v>
+        <v>0.6749999999999999</v>
       </c>
       <c r="AE2">
-        <v>0.72</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="AF2">
-        <v>0.72</v>
+        <v>0.665</v>
       </c>
       <c r="AG2">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="AH2">
-        <v>0.7200000000000001</v>
+        <v>0.655</v>
       </c>
       <c r="AI2">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="AJ2">
-        <v>0.72</v>
+        <v>0.645</v>
       </c>
       <c r="AK2">
-        <v>0.72</v>
+        <v>0.6399999999999999</v>
       </c>
       <c r="AL2">
-        <v>0.72</v>
+        <v>0.635</v>
       </c>
       <c r="AM2">
-        <v>0.72</v>
+        <v>0.6299999999999999</v>
       </c>
       <c r="AN2">
-        <v>0.72</v>
+        <v>0.6249999999999999</v>
       </c>
       <c r="AO2">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="AP2">
-        <v>0.72</v>
+        <v>0.615</v>
       </c>
       <c r="AQ2">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="AR2">
-        <v>0.72</v>
+        <v>0.605</v>
       </c>
       <c r="AS2">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="AT2">
-        <v>0.72</v>
+        <v>0.595</v>
       </c>
       <c r="AU2">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="AV2">
-        <v>0.72</v>
+        <v>0.585</v>
       </c>
       <c r="AW2">
-        <v>0.72</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="AX2">
-        <v>0.72</v>
+        <v>0.575</v>
       </c>
       <c r="AY2">
-        <v>0.72</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="AZ2">
-        <v>0.72</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="BA2">
-        <v>0.72</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BB2">
-        <v>0.72</v>
+        <v>0.5549999999999999</v>
       </c>
       <c r="BC2">
-        <v>0.72</v>
+        <v>0.55</v>
       </c>
       <c r="BD2">
-        <v>0.72</v>
+        <v>0.545</v>
       </c>
       <c r="BE2">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="BF2">
-        <v>0.72</v>
+        <v>0.535</v>
       </c>
       <c r="BG2">
-        <v>0.72</v>
+        <v>0.53</v>
       </c>
       <c r="BH2">
-        <v>0.72</v>
+        <v>0.525</v>
       </c>
       <c r="BI2">
-        <v>0.72</v>
+        <v>0.52</v>
       </c>
       <c r="BJ2">
-        <v>0.72</v>
+        <v>0.515</v>
       </c>
       <c r="BK2">
-        <v>0.72</v>
+        <v>0.51</v>
       </c>
       <c r="BL2">
-        <v>0.72</v>
+        <v>0.505</v>
       </c>
       <c r="BM2">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
